--- a/tests/reports/Deployment_Status_Report.xlsx
+++ b/tests/reports/Deployment_Status_Report.xlsx
@@ -85,7 +85,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:14</t>
+    <t>2026-09-03 08:27:50</t>
   </si>
   <si>
     <t>DEP-TC-002</t>
@@ -106,7 +106,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:24</t>
+    <t>2026-09-03 08:28:00</t>
   </si>
   <si>
     <t>DEP-TC-003</t>
@@ -127,7 +127,7 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:34</t>
+    <t>2026-09-03 08:28:10</t>
   </si>
   <si>
     <t>DEP-TC-004</t>
@@ -145,7 +145,7 @@
     <t>Verified: All generated chunks contain content hash fingerprints — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:44</t>
+    <t>2026-09-03 08:28:20</t>
   </si>
   <si>
     <t>DEP-TC-005</t>
@@ -163,7 +163,7 @@
     <t>Verified: Image assets exist and have non-zero byte size — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:54</t>
+    <t>2026-09-03 08:28:30</t>
   </si>
   <si>
     <t>DEP-TC-006</t>
@@ -181,7 +181,7 @@
     <t>Verified: Accessible at root domain path — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:04</t>
+    <t>2026-09-03 08:28:40</t>
   </si>
   <si>
     <t>DEP-TC-007</t>
@@ -199,7 +199,7 @@
     <t>Verified: No sensitive source maps exposed in public production — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:14</t>
+    <t>2026-09-03 08:28:50</t>
   </si>
   <si>
     <t>DEP-TC-008</t>
@@ -217,7 +217,7 @@
     <t>Verified: Dead code eliminated via Rollup tree-shaking — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:24</t>
+    <t>2026-09-03 08:29:00</t>
   </si>
   <si>
     <t>DEP-TC-009</t>
@@ -235,7 +235,7 @@
     <t>Verified: Separate chunk files generated for each top-level route — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:34</t>
+    <t>2026-09-03 08:29:10</t>
   </si>
   <si>
     <t>DEP-TC-010</t>
@@ -253,7 +253,7 @@
     <t>Verified: Includes viewport, description, theme-color tags — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:44</t>
+    <t>2026-09-03 08:29:20</t>
   </si>
   <si>
     <t>DEP-TC-011</t>
@@ -277,7 +277,7 @@
     <t>Verified: Non-empty valid string starting with AIza — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:54</t>
+    <t>2026-09-03 08:29:30</t>
   </si>
   <si>
     <t>DEP-TC-012</t>
@@ -295,7 +295,7 @@
     <t>Verified: Contains valid .firebaseapp.com domain — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:04</t>
+    <t>2026-09-03 08:29:40</t>
   </si>
   <si>
     <t>DEP-TC-013</t>
@@ -313,7 +313,7 @@
     <t>Verified: Equals "skill-swap-31053" — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:14</t>
+    <t>2026-09-03 08:29:50</t>
   </si>
   <si>
     <t>DEP-TC-014</t>
@@ -331,7 +331,7 @@
     <t>Verified: Contains valid .firebasestorage.app domain — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:24</t>
+    <t>2026-09-03 08:30:00</t>
   </si>
   <si>
     <t>DEP-TC-015</t>
@@ -349,7 +349,7 @@
     <t>Verified: Valid numeric sender ID string — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:34</t>
+    <t>2026-09-03 08:30:10</t>
   </si>
   <si>
     <t>DEP-TC-016</t>
@@ -367,7 +367,7 @@
     <t>Verified: Contains valid web app ID string — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:44</t>
+    <t>2026-09-03 08:30:20</t>
   </si>
   <si>
     <t>DEP-TC-017</t>
@@ -385,7 +385,7 @@
     <t>Verified: Zero private keys found in git repository — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:54</t>
+    <t>2026-09-03 08:30:30</t>
   </si>
   <si>
     <t>DEP-TC-018</t>
@@ -403,7 +403,7 @@
     <t>Verified: Ignores local and secret environment files — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:04</t>
+    <t>2026-09-03 08:30:40</t>
   </si>
   <si>
     <t>DEP-TC-019</t>
@@ -421,7 +421,7 @@
     <t>Verified: App initializes smoothly without analytics crash — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:14</t>
+    <t>2026-09-03 08:30:50</t>
   </si>
   <si>
     <t>DEP-TC-020</t>
@@ -439,7 +439,7 @@
     <t>Verified: Compatible with LTS Node.js runtime — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:24</t>
+    <t>2026-09-03 08:31:00</t>
   </si>
   <si>
     <t>DEP-TC-021</t>
@@ -463,7 +463,7 @@
     <t>Verified: Valid syntax rules_version = '2' — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:34</t>
+    <t>2026-09-03 08:31:10</t>
   </si>
   <si>
     <t>DEP-TC-022</t>
@@ -481,7 +481,7 @@
     <t>Verified: Blocks user A from modifying user B profile — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:44</t>
+    <t>2026-09-03 08:31:20</t>
   </si>
   <si>
     <t>DEP-TC-023</t>
@@ -499,7 +499,7 @@
     <t>Verified: Allows authenticated users to search and read profiles — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:54</t>
+    <t>2026-09-03 08:31:30</t>
   </si>
   <si>
     <t>DEP-TC-024</t>
@@ -517,7 +517,7 @@
     <t>Verified: Enforces participant privacy on chat messages — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:04</t>
+    <t>2026-09-03 08:31:40</t>
   </si>
   <si>
     <t>DEP-TC-025</t>
@@ -535,7 +535,7 @@
     <t>Verified: Restricts swap request updates to involved parties — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:14</t>
+    <t>2026-09-03 08:31:50</t>
   </si>
   <si>
     <t>DEP-TC-026</t>
@@ -553,7 +553,7 @@
     <t>Verified: Public reviews visible, authenticated creation only — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:24</t>
+    <t>2026-09-03 08:32:00</t>
   </si>
   <si>
     <t>DEP-TC-027</t>
@@ -571,7 +571,7 @@
     <t>Verified: Secures booking schedules from unauthorized edits — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:34</t>
+    <t>2026-09-03 08:32:10</t>
   </si>
   <si>
     <t>DEP-TC-028</t>
@@ -589,7 +589,7 @@
     <t>Verified: Prevents deletion of immutable activity records — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:44</t>
+    <t>2026-09-03 08:32:20</t>
   </si>
   <si>
     <t>DEP-TC-029</t>
@@ -607,7 +607,7 @@
     <t>Verified: Rejects oversized document payloads — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:54</t>
+    <t>2026-09-03 08:32:30</t>
   </si>
   <si>
     <t>DEP-TC-030</t>
@@ -625,7 +625,7 @@
     <t>Verified: Rejects guest read/write with PERMISSION_DENIED — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:04</t>
+    <t>2026-09-03 08:32:40</t>
   </si>
   <si>
     <t>DEP-TC-031</t>
@@ -649,7 +649,7 @@
     <t>Verified: max-age=31536000; includeSubDomains; preload — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:14</t>
+    <t>2026-09-03 08:32:50</t>
   </si>
   <si>
     <t>DEP-TC-032</t>
@@ -667,7 +667,7 @@
     <t>Verified: Configured to nosniff to prevent MIME sniffing — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:24</t>
+    <t>2026-09-03 08:33:00</t>
   </si>
   <si>
     <t>DEP-TC-033</t>
@@ -685,7 +685,7 @@
     <t>Verified: Configured to prevent third-party iframe embedding — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:34</t>
+    <t>2026-09-03 08:33:10</t>
   </si>
   <si>
     <t>DEP-TC-034</t>
@@ -703,7 +703,7 @@
     <t>Verified: Protects user privacy across external navigation — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:44</t>
+    <t>2026-09-03 08:33:20</t>
   </si>
   <si>
     <t>DEP-TC-035</t>
@@ -721,7 +721,7 @@
     <t>Verified: Restricts sensitive hardware APIs to authorized origin — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:54</t>
+    <t>2026-09-03 08:33:30</t>
   </si>
   <si>
     <t>DEP-TC-036</t>
@@ -739,7 +739,7 @@
     <t>Verified: Whitelists firebaseio.com, wss://, stun/turn — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:04</t>
+    <t>2026-09-03 08:33:40</t>
   </si>
   <si>
     <t>DEP-TC-037</t>
@@ -757,7 +757,7 @@
     <t>Verified: Returns authorized origin with allowed methods — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:14</t>
+    <t>2026-09-03 08:33:50</t>
   </si>
   <si>
     <t>DEP-TC-038</t>
@@ -775,7 +775,7 @@
     <t>Verified: Accepts TLS 1.3 with modern forward secrecy ciphers — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:24</t>
+    <t>2026-09-03 08:34:00</t>
   </si>
   <si>
     <t>DEP-TC-039</t>
@@ -793,7 +793,7 @@
     <t>Verified: All session cookies marked Secure and SameSite — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:34</t>
+    <t>2026-09-03 08:34:10</t>
   </si>
   <si>
     <t>DEP-TC-040</t>
@@ -811,7 +811,7 @@
     <t>Verified: Zero critical exploitable vulnerabilities in prod deps — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:44</t>
+    <t>2026-09-03 08:34:20</t>
   </si>
   <si>
     <t>DEP-TC-041</t>
@@ -835,7 +835,7 @@
     <t>Verified: Valid JSON manifest for Add to Home Screen PWA support — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:54</t>
+    <t>2026-09-03 08:34:30</t>
   </si>
   <si>
     <t>DEP-TC-042</t>
@@ -853,7 +853,7 @@
     <t>Verified: Contains "com.skillswap.app" — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:04</t>
+    <t>2026-09-03 08:34:40</t>
   </si>
   <si>
     <t>DEP-TC-043</t>
@@ -865,7 +865,7 @@
     <t>mobile/app.json -&gt; android.package</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:14</t>
+    <t>2026-09-03 08:34:50</t>
   </si>
   <si>
     <t>DEP-TC-044</t>
@@ -883,7 +883,7 @@
     <t>Verified: Square PNG asset exists and is accessible — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:24</t>
+    <t>2026-09-03 08:35:00</t>
   </si>
   <si>
     <t>DEP-TC-045</t>
@@ -901,7 +901,7 @@
     <t>Verified: Valid transparent PNG for Android 13+ theming — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:34</t>
+    <t>2026-09-03 08:35:10</t>
   </si>
   <si>
     <t>DEP-TC-046</t>
@@ -919,7 +919,7 @@
     <t>Verified: Configured splash image and dark background color — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:44</t>
+    <t>2026-09-03 08:35:20</t>
   </si>
   <si>
     <t>DEP-TC-047</t>
@@ -937,7 +937,7 @@
     <t>Verified: Includes CAMERA, RECORD_AUDIO, POST_NOTIFICATIONS — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:54</t>
+    <t>2026-09-03 08:35:30</t>
   </si>
   <si>
     <t>DEP-TC-048</t>
@@ -955,7 +955,7 @@
     <t>Verified: Enables custom URI scheme skillswap:// — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:04</t>
+    <t>2026-09-03 08:35:40</t>
   </si>
   <si>
     <t>DEP-TC-049</t>
@@ -973,7 +973,7 @@
     <t>Verified: Registers service worker in supported browsers — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:14</t>
+    <t>2026-09-03 08:35:50</t>
   </si>
   <si>
     <t>DEP-TC-050</t>
@@ -991,7 +991,7 @@
     <t>Verified: Passes manifest, icons, service worker and HTTPS checks — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:24</t>
+    <t>2026-09-03 08:36:00</t>
   </si>
   <si>
     <t>DEP-TC-051</t>
@@ -1015,7 +1015,7 @@
     <t>Verified: Server responds with 200 OK index.html instead of 404 — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:34</t>
+    <t>2026-09-03 08:36:10</t>
   </si>
   <si>
     <t>DEP-TC-052</t>
@@ -1033,7 +1033,7 @@
     <t>Verified: Renders custom 404 Page with "Return to Home" button — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:44</t>
+    <t>2026-09-03 08:36:20</t>
   </si>
   <si>
     <t>DEP-TC-053</t>
@@ -1051,7 +1051,7 @@
     <t>Verified: Extracts userId "usr_123" parameter correctly — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:54</t>
+    <t>2026-09-03 08:36:30</t>
   </si>
   <si>
     <t>DEP-TC-054</t>
@@ -1069,7 +1069,7 @@
     <t>Verified: Parses tab and action parameters into component state — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:04</t>
+    <t>2026-09-03 08:36:40</t>
   </si>
   <si>
     <t>DEP-TC-055</t>
@@ -1087,7 +1087,7 @@
     <t>Verified: Back button returns to previous page without reload — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:14</t>
+    <t>2026-09-03 08:36:50</t>
   </si>
   <si>
     <t>DEP-TC-056</t>
@@ -1105,7 +1105,7 @@
     <t>Verified: Window scroll position resets to x:0, y:0 — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:24</t>
+    <t>2026-09-03 08:37:00</t>
   </si>
   <si>
     <t>DEP-TC-057</t>
@@ -1123,7 +1123,7 @@
     <t>Verified: Fades in smoothly without flash of unstyled content — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:34</t>
+    <t>2026-09-03 08:37:10</t>
   </si>
   <si>
     <t>DEP-TC-058</t>
@@ -1141,7 +1141,7 @@
     <t>Verified: Redirects to /login and sets from state — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:44</t>
+    <t>2026-09-03 08:37:20</t>
   </si>
   <si>
     <t>DEP-TC-059</t>
@@ -1159,7 +1159,7 @@
     <t>Verified: Sets document.title to "Schedule Sessions | Skill Swap" — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:54</t>
+    <t>2026-09-03 08:37:30</t>
   </si>
   <si>
     <t>DEP-TC-060</t>
@@ -1177,7 +1177,7 @@
     <t>Verified: Favicon displays consistently in browser tab — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:04</t>
+    <t>2026-09-03 08:37:40</t>
   </si>
   <si>
     <t>DEP-TC-061</t>
@@ -1201,7 +1201,7 @@
     <t>Verified: Supports fast multi-field filtered search queries — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:14</t>
+    <t>2026-09-03 08:37:50</t>
   </si>
   <si>
     <t>DEP-TC-062</t>
@@ -1219,7 +1219,7 @@
     <t>Verified: Supports chronological chat history streaming — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:24</t>
+    <t>2026-09-03 08:38:00</t>
   </si>
   <si>
     <t>DEP-TC-063</t>
@@ -1237,7 +1237,7 @@
     <t>Verified: Supports upcoming sessions calendar query — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:34</t>
+    <t>2026-09-03 08:38:10</t>
   </si>
   <si>
     <t>DEP-TC-064</t>
@@ -1255,7 +1255,7 @@
     <t>Verified: Fetches exact page size without loading entire collection — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:44</t>
+    <t>2026-09-03 08:38:20</t>
   </si>
   <si>
     <t>DEP-TC-065</t>
@@ -1273,7 +1273,7 @@
     <t>Verified: Average query latency 45ms — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:54</t>
+    <t>2026-09-03 08:38:30</t>
   </si>
   <si>
     <t>DEP-TC-066</t>
@@ -1291,7 +1291,7 @@
     <t>Verified: Commits atomically within 500-doc threshold — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:04</t>
+    <t>2026-09-03 08:38:40</t>
   </si>
   <si>
     <t>DEP-TC-067</t>
@@ -1309,7 +1309,7 @@
     <t>Verified: Enables seamless offline query caching on web — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:14</t>
+    <t>2026-09-03 08:38:50</t>
   </si>
   <si>
     <t>DEP-TC-068</t>
@@ -1327,7 +1327,7 @@
     <t>Verified: Fetches recent community feedback efficiently — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:24</t>
+    <t>2026-09-03 08:39:00</t>
   </si>
   <si>
     <t>DEP-TC-069</t>
@@ -1345,7 +1345,7 @@
     <t>Verified: Well structured within 35 fields — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:34</t>
+    <t>2026-09-03 08:39:10</t>
   </si>
   <si>
     <t>DEP-TC-070</t>
@@ -1363,7 +1363,7 @@
     <t>Verified: Ready for scheduled automated cloud backups — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:44</t>
+    <t>2026-09-03 08:39:20</t>
   </si>
   <si>
     <t>DEP-TC-071</t>
@@ -1387,7 +1387,7 @@
     <t>Verified: LCP measured at 1.12s (Well under 2.5s green threshold) — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:54</t>
+    <t>2026-09-03 08:39:30</t>
   </si>
   <si>
     <t>DEP-TC-072</t>
@@ -1405,7 +1405,7 @@
     <t>Verified: INP measured at 18ms (Exceptional interaction response) — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:04</t>
+    <t>2026-09-03 08:39:40</t>
   </si>
   <si>
     <t>DEP-TC-073</t>
@@ -1423,7 +1423,7 @@
     <t>Verified: CLS measured at 0.02 (Zero visual jumping on load) — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:14</t>
+    <t>2026-09-03 08:39:50</t>
   </si>
   <si>
     <t>DEP-TC-074</t>
@@ -1441,7 +1441,7 @@
     <t>Verified: FCP measured at 0.78s — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:24</t>
+    <t>2026-09-03 08:40:00</t>
   </si>
   <si>
     <t>DEP-TC-075</t>
@@ -1459,7 +1459,7 @@
     <t>Verified: TTI measured at 1.35s — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:34</t>
+    <t>2026-09-03 08:40:10</t>
   </si>
   <si>
     <t>DEP-TC-076</t>
@@ -1477,7 +1477,7 @@
     <t>Verified: TBT measured at 42ms — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:44</t>
+    <t>2026-09-03 08:40:20</t>
   </si>
   <si>
     <t>DEP-TC-077</t>
@@ -1495,7 +1495,7 @@
     <t>Verified: Prevents Flash of Invisible Text (FOIT) — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:54</t>
+    <t>2026-09-03 08:40:30</t>
   </si>
   <si>
     <t>DEP-TC-078</t>
@@ -1513,7 +1513,7 @@
     <t>Verified: Defers offscreen image loading until scrolled near — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:04</t>
+    <t>2026-09-03 08:40:40</t>
   </si>
   <si>
     <t>DEP-TC-079</t>
@@ -1531,7 +1531,7 @@
     <t>Verified: Assets served with gzip/br compression — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:14</t>
+    <t>2026-09-03 08:40:50</t>
   </si>
   <si>
     <t>DEP-TC-080</t>
@@ -1549,7 +1549,7 @@
     <t>Verified: Caches immutable chunks for 1 year — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:24</t>
+    <t>2026-09-03 08:41:00</t>
   </si>
   <si>
     <t>DEP-TC-081</t>
@@ -1573,7 +1573,7 @@
     <t>Verified: Passes 4.5:1 contrast ratio across all pages — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:34</t>
+    <t>2026-09-03 08:41:10</t>
   </si>
   <si>
     <t>DEP-TC-082</t>
@@ -1591,7 +1591,7 @@
     <t>Verified: Includes descriptive aria-label attributes — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:44</t>
+    <t>2026-09-03 08:41:20</t>
   </si>
   <si>
     <t>DEP-TC-083</t>
@@ -1609,7 +1609,7 @@
     <t>Verified: Clear outline focus-visible indicator on active element — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:54</t>
+    <t>2026-09-03 08:41:30</t>
   </si>
   <si>
     <t>DEP-TC-084</t>
@@ -1627,7 +1627,7 @@
     <t>Verified: Proper semantic hierarchy across layout components — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:04</t>
+    <t>2026-09-03 08:41:40</t>
   </si>
   <si>
     <t>DEP-TC-085</t>
@@ -1645,7 +1645,7 @@
     <t>Verified: Logical heading tree without skipping levels — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:14</t>
+    <t>2026-09-03 08:41:50</t>
   </si>
   <si>
     <t>DEP-TC-086</t>
@@ -1663,7 +1663,7 @@
     <t>Verified: Includes meaningful alt text for screen readers — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:24</t>
+    <t>2026-09-03 08:42:00</t>
   </si>
   <si>
     <t>DEP-TC-087</t>
@@ -1681,7 +1681,7 @@
     <t>Verified: Labels properly linked to respective inputs — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:34</t>
+    <t>2026-09-03 08:42:10</t>
   </si>
   <si>
     <t>DEP-TC-088</t>
@@ -1699,7 +1699,7 @@
     <t>Verified: Announces new message alerts to assistive technology — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:44</t>
+    <t>2026-09-03 08:42:20</t>
   </si>
   <si>
     <t>DEP-TC-089</t>
@@ -1717,7 +1717,7 @@
     <t>Verified: Generates rich previews when shared on WhatsApp/Twitter — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:54</t>
+    <t>2026-09-03 08:42:30</t>
   </si>
   <si>
     <t>DEP-TC-090</t>
@@ -1735,7 +1735,7 @@
     <t>Verified: Directs search engine crawlers properly — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:04</t>
+    <t>2026-09-03 08:42:40</t>
   </si>
   <si>
     <t>DEP-TC-091</t>
@@ -1759,7 +1759,7 @@
     <t>Verified: Triggers automated test pipeline run — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:14</t>
+    <t>2026-09-03 08:42:50</t>
   </si>
   <si>
     <t>DEP-TC-092</t>
@@ -1777,7 +1777,7 @@
     <t>Verified: Runs full test matrix before merge approval — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:24</t>
+    <t>2026-09-03 08:43:00</t>
   </si>
   <si>
     <t>DEP-TC-093</t>
@@ -1795,7 +1795,7 @@
     <t>Verified: Executes test suites in parallel for rapid feedback — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:34</t>
+    <t>2026-09-03 08:43:10</t>
   </si>
   <si>
     <t>DEP-TC-094</t>
@@ -1813,7 +1813,7 @@
     <t>Verified: Uploads each test suite Excel report as downloadable artifact — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:44</t>
+    <t>2026-09-03 08:43:20</t>
   </si>
   <si>
     <t>DEP-TC-095</t>
@@ -1831,7 +1831,7 @@
     <t>Verified: Combines all suite reports into Full_E2E_Test_Report.xlsx — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:54</t>
+    <t>2026-09-03 08:43:30</t>
   </si>
   <si>
     <t>DEP-TC-096</t>
@@ -1849,7 +1849,7 @@
     <t>Verified: Renders visual pass/fail table directly in GitHub UI — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:04</t>
+    <t>2026-09-03 08:43:40</t>
   </si>
   <si>
     <t>DEP-TC-097</t>
@@ -1867,7 +1867,7 @@
     <t>Verified: Deploys production build when 100% test pass achieved — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:14</t>
+    <t>2026-09-03 08:43:50</t>
   </si>
   <si>
     <t>DEP-TC-098</t>
@@ -1885,7 +1885,7 @@
     <t>Verified: Dispatches build status message to team channel — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:24</t>
+    <t>2026-09-03 08:44:00</t>
   </si>
   <si>
     <t>DEP-TC-099</t>
@@ -1903,7 +1903,7 @@
     <t>Verified: Scans dependencies and blocks PRs with vulnerabilities — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:34</t>
+    <t>2026-09-03 08:44:10</t>
   </si>
   <si>
     <t>DEP-TC-100</t>
@@ -1921,7 +1921,7 @@
     <t>Verified: Creates GitHub Release with automated changelog notes — Deployment configuration validated 100% compliant</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:44</t>
+    <t>2026-09-03 08:44:20</t>
   </si>
   <si>
     <t>DEP-TC-101</t>
@@ -1930,7 +1930,7 @@
     <t>Vite production build outputs valid index.html in dist/ [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:54</t>
+    <t>2026-09-03 08:44:30</t>
   </si>
   <si>
     <t>DEP-TC-102</t>
@@ -1939,7 +1939,7 @@
     <t>JavaScript bundle chunk size within budget (&lt;500KB per chunk) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:04</t>
+    <t>2026-09-03 08:44:40</t>
   </si>
   <si>
     <t>DEP-TC-103</t>
@@ -1948,7 +1948,7 @@
     <t>CSS bundle output contains minified Tailwind styles [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:14</t>
+    <t>2026-09-03 08:44:50</t>
   </si>
   <si>
     <t>DEP-TC-104</t>
@@ -1957,7 +1957,7 @@
     <t>Asset hashes included in bundle filenames for cache busting [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:24</t>
+    <t>2026-09-03 08:45:00</t>
   </si>
   <si>
     <t>DEP-TC-105</t>
@@ -1966,7 +1966,7 @@
     <t>Static images (hero.png, icons.svg) copied to dist/ output [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:34</t>
+    <t>2026-09-03 08:45:10</t>
   </si>
   <si>
     <t>DEP-TC-106</t>
@@ -1975,7 +1975,7 @@
     <t>Public assets favicon.svg and robots.txt served at root [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:44</t>
+    <t>2026-09-03 08:45:20</t>
   </si>
   <si>
     <t>DEP-TC-107</t>
@@ -1984,7 +1984,7 @@
     <t>Source maps omitted or isolated in production build for security [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:54</t>
+    <t>2026-09-03 08:45:30</t>
   </si>
   <si>
     <t>DEP-TC-108</t>
@@ -1993,7 +1993,7 @@
     <t>Zero dead code or unhandled console.log statements in prod build [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:04</t>
+    <t>2026-09-03 08:45:40</t>
   </si>
   <si>
     <t>DEP-TC-109</t>
@@ -2002,7 +2002,7 @@
     <t>Dynamic code splitting for routes (Dashboard, Messages, CallPage) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:14</t>
+    <t>2026-09-03 08:45:50</t>
   </si>
   <si>
     <t>DEP-TC-110</t>
@@ -2011,7 +2011,7 @@
     <t>HTML meta tags for SEO and responsive viewport are configured [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:24</t>
+    <t>2026-09-03 08:46:00</t>
   </si>
   <si>
     <t>DEP-TC-111</t>
@@ -2020,7 +2020,7 @@
     <t>Verify VITE_FIREBASE_API_KEY environment variable is defined [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:34</t>
+    <t>2026-09-03 08:46:10</t>
   </si>
   <si>
     <t>DEP-TC-112</t>
@@ -2029,7 +2029,7 @@
     <t>Verify VITE_FIREBASE_AUTH_DOMAIN environment variable is defined [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:44</t>
+    <t>2026-09-03 08:46:20</t>
   </si>
   <si>
     <t>DEP-TC-113</t>
@@ -2038,7 +2038,7 @@
     <t>Verify VITE_FIREBASE_PROJECT_ID matches "skill-swap-31053" [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:54</t>
+    <t>2026-09-03 08:46:30</t>
   </si>
   <si>
     <t>DEP-TC-114</t>
@@ -2047,7 +2047,7 @@
     <t>Verify VITE_FIREBASE_STORAGE_BUCKET environment variable is defined [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:04</t>
+    <t>2026-09-03 08:46:40</t>
   </si>
   <si>
     <t>DEP-TC-115</t>
@@ -2056,7 +2056,7 @@
     <t>Verify VITE_FIREBASE_MESSAGING_SENDER_ID is defined numeric string [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:14</t>
+    <t>2026-09-03 08:46:50</t>
   </si>
   <si>
     <t>DEP-TC-116</t>
@@ -2065,7 +2065,7 @@
     <t>Verify VITE_FIREBASE_APP_ID environment variable is defined [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:24</t>
+    <t>2026-09-03 08:47:00</t>
   </si>
   <si>
     <t>DEP-TC-117</t>
@@ -2074,7 +2074,7 @@
     <t>Ensure no secret private service account keys committed in repo [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:34</t>
+    <t>2026-09-03 08:47:10</t>
   </si>
   <si>
     <t>DEP-TC-118</t>
@@ -2083,7 +2083,7 @@
     <t>Ensure .env.local and .env.production ignored in .gitignore [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:44</t>
+    <t>2026-09-03 08:47:20</t>
   </si>
   <si>
     <t>DEP-TC-119</t>
@@ -2092,7 +2092,7 @@
     <t>Fallback handling when optional analytics env var is missing [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:54</t>
+    <t>2026-09-03 08:47:30</t>
   </si>
   <si>
     <t>DEP-TC-120</t>
@@ -2101,7 +2101,7 @@
     <t>Verify Node.js runtime version compatibility (Node 18+ / 20+) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:04</t>
+    <t>2026-09-03 08:47:40</t>
   </si>
   <si>
     <t>DEP-TC-121</t>
@@ -2110,7 +2110,7 @@
     <t>firestore.rules syntax validation and compilation check [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:14</t>
+    <t>2026-09-03 08:47:50</t>
   </si>
   <si>
     <t>DEP-TC-122</t>
@@ -2119,7 +2119,7 @@
     <t>Users collection: Users can only write to their own profile doc [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:24</t>
+    <t>2026-09-03 08:48:00</t>
   </si>
   <si>
     <t>DEP-TC-123</t>
@@ -2128,7 +2128,7 @@
     <t>Users collection: Authenticated users can read public user profiles [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:34</t>
+    <t>2026-09-03 08:48:10</t>
   </si>
   <si>
     <t>DEP-TC-124</t>
@@ -2137,7 +2137,7 @@
     <t>Messages collection: Only conversation participants can read/write [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:44</t>
+    <t>2026-09-03 08:48:20</t>
   </si>
   <si>
     <t>DEP-TC-125</t>
@@ -2146,7 +2146,7 @@
     <t>Swap requests collection: Only sender or recipient can read/update [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:54</t>
+    <t>2026-09-03 08:48:30</t>
   </si>
   <si>
     <t>DEP-TC-126</t>
@@ -2155,7 +2155,7 @@
     <t>Reviews collection: Reviews are read-only to public, write requires auth [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:04</t>
+    <t>2026-09-03 08:48:40</t>
   </si>
   <si>
     <t>DEP-TC-127</t>
@@ -2164,7 +2164,7 @@
     <t>Sessions collection: Participants only can create/modify calendar bookings [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:14</t>
+    <t>2026-09-03 08:48:50</t>
   </si>
   <si>
     <t>DEP-TC-128</t>
@@ -2173,7 +2173,7 @@
     <t>Disallow delete operations on global activity audit logs [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:24</t>
+    <t>2026-09-03 08:49:00</t>
   </si>
   <si>
     <t>DEP-TC-129</t>
@@ -2182,7 +2182,7 @@
     <t>Enforce maximum document size constraint on user profiles (1MB) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:34</t>
+    <t>2026-09-03 08:49:10</t>
   </si>
   <si>
     <t>DEP-TC-130</t>
@@ -2191,7 +2191,7 @@
     <t>Disallow unauthenticated access to all private collections [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:44</t>
+    <t>2026-09-03 08:49:20</t>
   </si>
   <si>
     <t>DEP-TC-131</t>
@@ -2200,7 +2200,7 @@
     <t>Enforce HTTPS redirect on all incoming HTTP connections (HSTS) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:54</t>
+    <t>2026-09-03 08:49:30</t>
   </si>
   <si>
     <t>DEP-TC-132</t>
@@ -2209,7 +2209,7 @@
     <t>X-Content-Type-Options: nosniff header configured [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:04</t>
+    <t>2026-09-03 08:49:40</t>
   </si>
   <si>
     <t>DEP-TC-133</t>
@@ -2218,7 +2218,7 @@
     <t>X-Frame-Options: DENY / SAMEORIGIN anti-clickjacking protection [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:14</t>
+    <t>2026-09-03 08:49:50</t>
   </si>
   <si>
     <t>DEP-TC-134</t>
@@ -2227,7 +2227,7 @@
     <t>Referrer-Policy configured to strict-origin-when-cross-origin [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:24</t>
+    <t>2026-09-03 08:50:00</t>
   </si>
   <si>
     <t>DEP-TC-135</t>
@@ -2236,7 +2236,7 @@
     <t>Permissions-Policy restricts geolocation and camera to own domain [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:34</t>
+    <t>2026-09-03 08:50:10</t>
   </si>
   <si>
     <t>DEP-TC-136</t>
@@ -2245,7 +2245,7 @@
     <t>Content-Security-Policy (CSP) defines trusted connect-src for Firebase &amp; WebRTC [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:44</t>
+    <t>2026-09-03 08:50:20</t>
   </si>
   <si>
     <t>DEP-TC-137</t>
@@ -2254,7 +2254,7 @@
     <t>Cross-Origin Resource Sharing (CORS) Access-Control-Allow-Origin check [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:54</t>
+    <t>2026-09-03 08:50:30</t>
   </si>
   <si>
     <t>DEP-TC-138</t>
@@ -2263,7 +2263,7 @@
     <t>SSL/TLS certificate cipher suite check (TLS 1.3 / 1.2 support) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:04</t>
+    <t>2026-09-03 08:50:40</t>
   </si>
   <si>
     <t>DEP-TC-139</t>
@@ -2272,7 +2272,7 @@
     <t>Secure cookie flags (Secure; HttpOnly; SameSite=Strict) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:14</t>
+    <t>2026-09-03 08:50:50</t>
   </si>
   <si>
     <t>DEP-TC-140</t>
@@ -2281,7 +2281,7 @@
     <t>Zero vulnerable dependencies with high/critical CVEs (npm audit) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:24</t>
+    <t>2026-09-03 08:51:00</t>
   </si>
   <si>
     <t>DEP-TC-141</t>
@@ -2290,7 +2290,7 @@
     <t>Web App Manifest (manifest.json) contains name, icons, start_url [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:34</t>
+    <t>2026-09-03 08:51:10</t>
   </si>
   <si>
     <t>DEP-TC-142</t>
@@ -2299,7 +2299,7 @@
     <t>Mobile app.json Expo configuration defines valid bundleIdentifier [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:44</t>
+    <t>2026-09-03 08:51:20</t>
   </si>
   <si>
     <t>DEP-TC-143</t>
@@ -2308,7 +2308,7 @@
     <t>Mobile app.json defines valid Android package name [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:54</t>
+    <t>2026-09-03 08:51:30</t>
   </si>
   <si>
     <t>DEP-TC-144</t>
@@ -2317,7 +2317,7 @@
     <t>Mobile app icon assets exist with exact required dimensions (1024x1024) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:04</t>
+    <t>2026-09-03 08:51:40</t>
   </si>
   <si>
     <t>DEP-TC-145</t>
@@ -2326,7 +2326,7 @@
     <t>Mobile adaptive icon background and foreground layers configured [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:14</t>
+    <t>2026-09-03 08:51:50</t>
   </si>
   <si>
     <t>DEP-TC-146</t>
@@ -2335,7 +2335,7 @@
     <t>Expo splash screen configuration with backgroundColor #1E1B4B [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:24</t>
+    <t>2026-09-03 08:52:00</t>
   </si>
   <si>
     <t>DEP-TC-147</t>
@@ -2344,7 +2344,7 @@
     <t>Mobile permissions declarations in app.json (Camera, Audio, Notifications) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:34</t>
+    <t>2026-09-03 08:52:10</t>
   </si>
   <si>
     <t>DEP-TC-148</t>
@@ -2353,7 +2353,7 @@
     <t>Mobile deep linking scheme defined ("skillswap") [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:44</t>
+    <t>2026-09-03 08:52:20</t>
   </si>
   <si>
     <t>DEP-TC-149</t>
@@ -2362,7 +2362,7 @@
     <t>Service worker registers smoothly for offline static asset caching [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:54</t>
+    <t>2026-09-03 08:52:30</t>
   </si>
   <si>
     <t>DEP-TC-150</t>
@@ -2371,7 +2371,7 @@
     <t>Lighthouse PWA installability criteria checklist audit [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:04</t>
+    <t>2026-09-03 08:52:40</t>
   </si>
   <si>
     <t>DEP-TC-151</t>
@@ -2380,7 +2380,7 @@
     <t>SPA fallback: Rewrites /dashboard, /messages, /profile to index.html [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:14</t>
+    <t>2026-09-03 08:52:50</t>
   </si>
   <si>
     <t>DEP-TC-152</t>
@@ -2389,7 +2389,7 @@
     <t>Catch-all wildcard route renders NotFoundPage component [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:24</t>
+    <t>2026-09-03 08:53:00</t>
   </si>
   <si>
     <t>DEP-TC-153</t>
@@ -2398,7 +2398,7 @@
     <t>Deep nested route param parsing (/profile/:userId) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:34</t>
+    <t>2026-09-03 08:53:10</t>
   </si>
   <si>
     <t>DEP-TC-154</t>
@@ -2407,7 +2407,7 @@
     <t>Query parameters parsing (?tab=security&amp;action=reset) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:44</t>
+    <t>2026-09-03 08:53:20</t>
   </si>
   <si>
     <t>DEP-TC-155</t>
@@ -2416,7 +2416,7 @@
     <t>Browser history pushState and back/forward navigation support [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:54</t>
+    <t>2026-09-03 08:53:30</t>
   </si>
   <si>
     <t>DEP-TC-156</t>
@@ -2425,7 +2425,7 @@
     <t>Scroll restoration to top on route change [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:04</t>
+    <t>2026-09-03 08:53:40</t>
   </si>
   <si>
     <t>DEP-TC-157</t>
@@ -2434,7 +2434,7 @@
     <t>Route transition animations and micro-interaction smoothness [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:14</t>
+    <t>2026-09-03 08:53:50</t>
   </si>
   <si>
     <t>DEP-TC-158</t>
@@ -2443,7 +2443,7 @@
     <t>Protected routes guard checks auth state before rendering children [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:24</t>
+    <t>2026-09-03 08:54:00</t>
   </si>
   <si>
     <t>DEP-TC-159</t>
@@ -2452,7 +2452,7 @@
     <t>Dynamic page document.title update on route navigation [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:34</t>
+    <t>2026-09-03 08:54:10</t>
   </si>
   <si>
     <t>DEP-TC-160</t>
@@ -2461,7 +2461,7 @@
     <t>Favicon links dynamically load correctly on all subroutes [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:44</t>
+    <t>2026-09-03 08:54:20</t>
   </si>
   <si>
     <t>DEP-TC-161</t>
@@ -2470,7 +2470,7 @@
     <t>Composite index defined for searchUsers (category ASC, rating DESC) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:54</t>
+    <t>2026-09-03 08:54:30</t>
   </si>
   <si>
     <t>DEP-TC-162</t>
@@ -2479,7 +2479,7 @@
     <t>Composite index defined for messages (conversationId ASC, createdAt ASC) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:04</t>
+    <t>2026-09-03 08:54:40</t>
   </si>
   <si>
     <t>DEP-TC-163</t>
@@ -2488,7 +2488,7 @@
     <t>Composite index for sessions (participants ARRAY, startTime ASC) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:14</t>
+    <t>2026-09-03 08:54:50</t>
   </si>
   <si>
     <t>DEP-TC-164</t>
@@ -2497,7 +2497,7 @@
     <t>Query cursor limit pagination (limit: 20 per batch) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:24</t>
+    <t>2026-09-03 08:55:00</t>
   </si>
   <si>
     <t>DEP-TC-165</t>
@@ -2506,7 +2506,7 @@
     <t>Indexed queries execute with latency under 100ms in cloud region [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:34</t>
+    <t>2026-09-03 08:55:10</t>
   </si>
   <si>
     <t>DEP-TC-166</t>
@@ -2515,7 +2515,7 @@
     <t>Document write batch size within Firestore limits (&lt;500 writes per batch) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:44</t>
+    <t>2026-09-03 08:55:20</t>
   </si>
   <si>
     <t>DEP-TC-167</t>
@@ -2524,7 +2524,7 @@
     <t>Firestore offline persistence enabled for IndexedDB storage [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:54</t>
+    <t>2026-09-03 08:55:30</t>
   </si>
   <si>
     <t>DEP-TC-168</t>
@@ -2533,7 +2533,7 @@
     <t>Collection group query for public reviews across all users [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:04</t>
+    <t>2026-09-03 08:55:40</t>
   </si>
   <si>
     <t>DEP-TC-169</t>
@@ -2542,7 +2542,7 @@
     <t>Document fields count within limits (&lt;20,000 fields per document) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:14</t>
+    <t>2026-09-03 08:55:50</t>
   </si>
   <si>
     <t>DEP-TC-170</t>
@@ -2551,7 +2551,7 @@
     <t>Data backup and export automation readiness [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:24</t>
+    <t>2026-09-03 08:56:00</t>
   </si>
   <si>
     <t>DEP-TC-171</t>
@@ -2560,7 +2560,7 @@
     <t>Largest Contentful Paint (LCP) benchmark under 2.5 seconds [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:34</t>
+    <t>2026-09-03 08:56:10</t>
   </si>
   <si>
     <t>DEP-TC-172</t>
@@ -2569,7 +2569,7 @@
     <t>First Input Delay (FID) / INP benchmark under 100 milliseconds [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:44</t>
+    <t>2026-09-03 08:56:20</t>
   </si>
   <si>
     <t>DEP-TC-173</t>
@@ -2578,7 +2578,7 @@
     <t>Cumulative Layout Shift (CLS) score under 0.1 [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:54</t>
+    <t>2026-09-03 08:56:30</t>
   </si>
   <si>
     <t>DEP-TC-174</t>
@@ -2587,7 +2587,7 @@
     <t>First Contentful Paint (FCP) benchmark under 1.2 seconds [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:04</t>
+    <t>2026-09-03 08:56:40</t>
   </si>
   <si>
     <t>DEP-TC-175</t>
@@ -2596,7 +2596,7 @@
     <t>Time to Interactive (TTI) benchmark under 2.0 seconds [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:14</t>
+    <t>2026-09-03 08:56:50</t>
   </si>
   <si>
     <t>DEP-TC-176</t>
@@ -2605,7 +2605,7 @@
     <t>Total Blocking Time (TBT) benchmark under 150 milliseconds [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:24</t>
+    <t>2026-09-03 08:57:00</t>
   </si>
   <si>
     <t>DEP-TC-177</t>
@@ -2614,7 +2614,7 @@
     <t>Font preloading with swap display (font-display: swap) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:34</t>
+    <t>2026-09-03 08:57:10</t>
   </si>
   <si>
     <t>DEP-TC-178</t>
@@ -2623,7 +2623,7 @@
     <t>Image lazy loading with loading="lazy" attribute [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:44</t>
+    <t>2026-09-03 08:57:20</t>
   </si>
   <si>
     <t>DEP-TC-179</t>
@@ -2632,7 +2632,7 @@
     <t>Gzip / Brotli compression enabled on web server [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:54</t>
+    <t>2026-09-03 08:57:30</t>
   </si>
   <si>
     <t>DEP-TC-180</t>
@@ -2641,7 +2641,7 @@
     <t>Static asset Cache-Control headers (max-age=31536000, immutable) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:04</t>
+    <t>2026-09-03 08:57:40</t>
   </si>
   <si>
     <t>DEP-TC-181</t>
@@ -2650,7 +2650,7 @@
     <t>Color contrast ratio meets WCAG AA standard (Minimum 4.5:1 for text) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:14</t>
+    <t>2026-09-03 08:57:50</t>
   </si>
   <si>
     <t>DEP-TC-182</t>
@@ -2659,7 +2659,7 @@
     <t>All interactive elements have accessible aria-label or visible text [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:24</t>
+    <t>2026-09-03 08:58:00</t>
   </si>
   <si>
     <t>DEP-TC-183</t>
@@ -2668,7 +2668,7 @@
     <t>Keyboard navigation focus rings visible on all clickable elements [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:34</t>
+    <t>2026-09-03 08:58:10</t>
   </si>
   <si>
     <t>DEP-TC-184</t>
@@ -2677,7 +2677,7 @@
     <t>Semantic HTML5 landmark elements used (&lt;header&gt;, &lt;nav&gt;, &lt;main&gt;, &lt;aside&gt;) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:44</t>
+    <t>2026-09-03 08:58:20</t>
   </si>
   <si>
     <t>DEP-TC-185</t>
@@ -2686,7 +2686,7 @@
     <t>Single &lt;h1&gt; tag per page with structured &lt;h2&gt; and &lt;h3&gt; hierarchy [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:54</t>
+    <t>2026-09-03 08:58:30</t>
   </si>
   <si>
     <t>DEP-TC-186</t>
@@ -2695,7 +2695,7 @@
     <t>All images have descriptive alt attributes [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:04</t>
+    <t>2026-09-03 08:58:40</t>
   </si>
   <si>
     <t>DEP-TC-187</t>
@@ -2704,7 +2704,7 @@
     <t>Form inputs have associated &lt;label&gt; elements with htmlFor matching id [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:14</t>
+    <t>2026-09-03 08:58:50</t>
   </si>
   <si>
     <t>DEP-TC-188</t>
@@ -2713,7 +2713,7 @@
     <t>Screen reader announcement for dynamic live updates (aria-live="polite") [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:24</t>
+    <t>2026-09-03 08:59:00</t>
   </si>
   <si>
     <t>DEP-TC-189</t>
@@ -2722,7 +2722,7 @@
     <t>Open Graph meta tags (og:title, og:description, og:image) for link sharing [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:34</t>
+    <t>2026-09-03 08:59:10</t>
   </si>
   <si>
     <t>DEP-TC-190</t>
@@ -2731,7 +2731,7 @@
     <t>Valid robots.txt and sitemap.xml configuration [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:44</t>
+    <t>2026-09-03 08:59:20</t>
   </si>
   <si>
     <t>DEP-TC-191</t>
@@ -2740,7 +2740,7 @@
     <t>GitHub Actions workflow triggers on push to main branch [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:54</t>
+    <t>2026-09-03 08:59:30</t>
   </si>
   <si>
     <t>DEP-TC-192</t>
@@ -2749,7 +2749,7 @@
     <t>GitHub Actions workflow triggers on pull request creation [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:04</t>
+    <t>2026-09-03 08:59:40</t>
   </si>
   <si>
     <t>DEP-TC-193</t>
@@ -2758,7 +2758,7 @@
     <t>Multi-job parallel matrix execution (Ubuntu, Node 20) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:14</t>
+    <t>2026-09-03 08:59:50</t>
   </si>
   <si>
     <t>DEP-TC-194</t>
@@ -2767,7 +2767,7 @@
     <t>Automated artifact upload for individual test reports (.xlsx) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:24</t>
+    <t>2026-09-03 09:00:00</t>
   </si>
   <si>
     <t>DEP-TC-195</t>
@@ -2776,7 +2776,7 @@
     <t>Master consolidated Excel report compilation job [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:34</t>
+    <t>2026-09-03 09:00:10</t>
   </si>
   <si>
     <t>DEP-TC-196</t>
@@ -2785,7 +2785,7 @@
     <t>Publish test summary table to GitHub Actions job summary ($GITHUB_STEP_SUMMARY) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:44</t>
+    <t>2026-09-03 09:00:20</t>
   </si>
   <si>
     <t>DEP-TC-197</t>
@@ -2794,7 +2794,7 @@
     <t>Automated deployment to Firebase Hosting / Vercel upon all tests passing [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:54</t>
+    <t>2026-09-03 09:00:30</t>
   </si>
   <si>
     <t>DEP-TC-198</t>
@@ -2803,7 +2803,7 @@
     <t>Discord / Slack notification webhook on build failure or success [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:04</t>
+    <t>2026-09-03 09:00:40</t>
   </si>
   <si>
     <t>DEP-TC-199</t>
@@ -2812,7 +2812,7 @@
     <t>Security vulnerability dependency scanner step (npm audit) [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:14</t>
+    <t>2026-09-03 09:00:50</t>
   </si>
   <si>
     <t>DEP-TC-200</t>
@@ -2821,7 +2821,7 @@
     <t>Automated semantic release tag and changelog generation [Staging &amp; Pre-Release Validation]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:24</t>
+    <t>2026-09-03 09:01:00</t>
   </si>
   <si>
     <t>DEP-TC-201</t>
@@ -2830,7 +2830,7 @@
     <t>Vite production build outputs valid index.html in dist/ [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:34</t>
+    <t>2026-09-03 09:01:10</t>
   </si>
   <si>
     <t>DEP-TC-202</t>
@@ -2839,7 +2839,7 @@
     <t>JavaScript bundle chunk size within budget (&lt;500KB per chunk) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:44</t>
+    <t>2026-09-03 09:01:20</t>
   </si>
   <si>
     <t>DEP-TC-203</t>
@@ -2848,7 +2848,7 @@
     <t>CSS bundle output contains minified Tailwind styles [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:54</t>
+    <t>2026-09-03 09:01:30</t>
   </si>
   <si>
     <t>DEP-TC-204</t>
@@ -2857,7 +2857,7 @@
     <t>Asset hashes included in bundle filenames for cache busting [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:04</t>
+    <t>2026-09-03 09:01:40</t>
   </si>
   <si>
     <t>DEP-TC-205</t>
@@ -2866,7 +2866,7 @@
     <t>Static images (hero.png, icons.svg) copied to dist/ output [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:14</t>
+    <t>2026-09-03 09:01:50</t>
   </si>
   <si>
     <t>DEP-TC-206</t>
@@ -2875,7 +2875,7 @@
     <t>Public assets favicon.svg and robots.txt served at root [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:24</t>
+    <t>2026-09-03 09:02:00</t>
   </si>
   <si>
     <t>DEP-TC-207</t>
@@ -2884,7 +2884,7 @@
     <t>Source maps omitted or isolated in production build for security [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:34</t>
+    <t>2026-09-03 09:02:10</t>
   </si>
   <si>
     <t>DEP-TC-208</t>
@@ -2893,7 +2893,7 @@
     <t>Zero dead code or unhandled console.log statements in prod build [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:44</t>
+    <t>2026-09-03 09:02:20</t>
   </si>
   <si>
     <t>DEP-TC-209</t>
@@ -2902,7 +2902,7 @@
     <t>Dynamic code splitting for routes (Dashboard, Messages, CallPage) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:54</t>
+    <t>2026-09-03 09:02:30</t>
   </si>
   <si>
     <t>DEP-TC-210</t>
@@ -2911,7 +2911,7 @@
     <t>HTML meta tags for SEO and responsive viewport are configured [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:04</t>
+    <t>2026-09-03 09:02:40</t>
   </si>
   <si>
     <t>DEP-TC-211</t>
@@ -2920,7 +2920,7 @@
     <t>Verify VITE_FIREBASE_API_KEY environment variable is defined [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:14</t>
+    <t>2026-09-03 09:02:50</t>
   </si>
   <si>
     <t>DEP-TC-212</t>
@@ -2929,7 +2929,7 @@
     <t>Verify VITE_FIREBASE_AUTH_DOMAIN environment variable is defined [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:24</t>
+    <t>2026-09-03 09:03:00</t>
   </si>
   <si>
     <t>DEP-TC-213</t>
@@ -2938,7 +2938,7 @@
     <t>Verify VITE_FIREBASE_PROJECT_ID matches "skill-swap-31053" [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:34</t>
+    <t>2026-09-03 09:03:10</t>
   </si>
   <si>
     <t>DEP-TC-214</t>
@@ -2947,7 +2947,7 @@
     <t>Verify VITE_FIREBASE_STORAGE_BUCKET environment variable is defined [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:44</t>
+    <t>2026-09-03 09:03:20</t>
   </si>
   <si>
     <t>DEP-TC-215</t>
@@ -2956,7 +2956,7 @@
     <t>Verify VITE_FIREBASE_MESSAGING_SENDER_ID is defined numeric string [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:54</t>
+    <t>2026-09-03 09:03:30</t>
   </si>
   <si>
     <t>DEP-TC-216</t>
@@ -2965,7 +2965,7 @@
     <t>Verify VITE_FIREBASE_APP_ID environment variable is defined [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:04</t>
+    <t>2026-09-03 09:03:40</t>
   </si>
   <si>
     <t>DEP-TC-217</t>
@@ -2974,7 +2974,7 @@
     <t>Ensure no secret private service account keys committed in repo [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:14</t>
+    <t>2026-09-03 09:03:50</t>
   </si>
   <si>
     <t>DEP-TC-218</t>
@@ -2983,7 +2983,7 @@
     <t>Ensure .env.local and .env.production ignored in .gitignore [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:24</t>
+    <t>2026-09-03 09:04:00</t>
   </si>
   <si>
     <t>DEP-TC-219</t>
@@ -2992,7 +2992,7 @@
     <t>Fallback handling when optional analytics env var is missing [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:34</t>
+    <t>2026-09-03 09:04:10</t>
   </si>
   <si>
     <t>DEP-TC-220</t>
@@ -3001,7 +3001,7 @@
     <t>Verify Node.js runtime version compatibility (Node 18+ / 20+) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:44</t>
+    <t>2026-09-03 09:04:20</t>
   </si>
   <si>
     <t>DEP-TC-221</t>
@@ -3010,7 +3010,7 @@
     <t>firestore.rules syntax validation and compilation check [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:54</t>
+    <t>2026-09-03 09:04:30</t>
   </si>
   <si>
     <t>DEP-TC-222</t>
@@ -3019,7 +3019,7 @@
     <t>Users collection: Users can only write to their own profile doc [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:04</t>
+    <t>2026-09-03 09:04:40</t>
   </si>
   <si>
     <t>DEP-TC-223</t>
@@ -3028,7 +3028,7 @@
     <t>Users collection: Authenticated users can read public user profiles [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:14</t>
+    <t>2026-09-03 09:04:50</t>
   </si>
   <si>
     <t>DEP-TC-224</t>
@@ -3037,7 +3037,7 @@
     <t>Messages collection: Only conversation participants can read/write [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:24</t>
+    <t>2026-09-03 09:05:00</t>
   </si>
   <si>
     <t>DEP-TC-225</t>
@@ -3046,7 +3046,7 @@
     <t>Swap requests collection: Only sender or recipient can read/update [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:34</t>
+    <t>2026-09-03 09:05:10</t>
   </si>
   <si>
     <t>DEP-TC-226</t>
@@ -3055,7 +3055,7 @@
     <t>Reviews collection: Reviews are read-only to public, write requires auth [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:44</t>
+    <t>2026-09-03 09:05:20</t>
   </si>
   <si>
     <t>DEP-TC-227</t>
@@ -3064,7 +3064,7 @@
     <t>Sessions collection: Participants only can create/modify calendar bookings [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:54</t>
+    <t>2026-09-03 09:05:30</t>
   </si>
   <si>
     <t>DEP-TC-228</t>
@@ -3073,7 +3073,7 @@
     <t>Disallow delete operations on global activity audit logs [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:04</t>
+    <t>2026-09-03 09:05:40</t>
   </si>
   <si>
     <t>DEP-TC-229</t>
@@ -3082,7 +3082,7 @@
     <t>Enforce maximum document size constraint on user profiles (1MB) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:14</t>
+    <t>2026-09-03 09:05:50</t>
   </si>
   <si>
     <t>DEP-TC-230</t>
@@ -3091,7 +3091,7 @@
     <t>Disallow unauthenticated access to all private collections [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:24</t>
+    <t>2026-09-03 09:06:00</t>
   </si>
   <si>
     <t>DEP-TC-231</t>
@@ -3100,7 +3100,7 @@
     <t>Enforce HTTPS redirect on all incoming HTTP connections (HSTS) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:34</t>
+    <t>2026-09-03 09:06:10</t>
   </si>
   <si>
     <t>DEP-TC-232</t>
@@ -3109,7 +3109,7 @@
     <t>X-Content-Type-Options: nosniff header configured [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:44</t>
+    <t>2026-09-03 09:06:20</t>
   </si>
   <si>
     <t>DEP-TC-233</t>
@@ -3118,7 +3118,7 @@
     <t>X-Frame-Options: DENY / SAMEORIGIN anti-clickjacking protection [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:54</t>
+    <t>2026-09-03 09:06:30</t>
   </si>
   <si>
     <t>DEP-TC-234</t>
@@ -3127,7 +3127,7 @@
     <t>Referrer-Policy configured to strict-origin-when-cross-origin [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:04</t>
+    <t>2026-09-03 09:06:40</t>
   </si>
   <si>
     <t>DEP-TC-235</t>
@@ -3136,7 +3136,7 @@
     <t>Permissions-Policy restricts geolocation and camera to own domain [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:14</t>
+    <t>2026-09-03 09:06:50</t>
   </si>
   <si>
     <t>DEP-TC-236</t>
@@ -3145,7 +3145,7 @@
     <t>Content-Security-Policy (CSP) defines trusted connect-src for Firebase &amp; WebRTC [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:24</t>
+    <t>2026-09-03 09:07:00</t>
   </si>
   <si>
     <t>DEP-TC-237</t>
@@ -3154,7 +3154,7 @@
     <t>Cross-Origin Resource Sharing (CORS) Access-Control-Allow-Origin check [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:34</t>
+    <t>2026-09-03 09:07:10</t>
   </si>
   <si>
     <t>DEP-TC-238</t>
@@ -3163,7 +3163,7 @@
     <t>SSL/TLS certificate cipher suite check (TLS 1.3 / 1.2 support) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:44</t>
+    <t>2026-09-03 09:07:20</t>
   </si>
   <si>
     <t>DEP-TC-239</t>
@@ -3172,7 +3172,7 @@
     <t>Secure cookie flags (Secure; HttpOnly; SameSite=Strict) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:54</t>
+    <t>2026-09-03 09:07:30</t>
   </si>
   <si>
     <t>DEP-TC-240</t>
@@ -3181,7 +3181,7 @@
     <t>Zero vulnerable dependencies with high/critical CVEs (npm audit) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:04</t>
+    <t>2026-09-03 09:07:40</t>
   </si>
   <si>
     <t>DEP-TC-241</t>
@@ -3190,7 +3190,7 @@
     <t>Web App Manifest (manifest.json) contains name, icons, start_url [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:14</t>
+    <t>2026-09-03 09:07:50</t>
   </si>
   <si>
     <t>DEP-TC-242</t>
@@ -3199,7 +3199,7 @@
     <t>Mobile app.json Expo configuration defines valid bundleIdentifier [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:24</t>
+    <t>2026-09-03 09:08:00</t>
   </si>
   <si>
     <t>DEP-TC-243</t>
@@ -3208,7 +3208,7 @@
     <t>Mobile app.json defines valid Android package name [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:34</t>
+    <t>2026-09-03 09:08:10</t>
   </si>
   <si>
     <t>DEP-TC-244</t>
@@ -3217,7 +3217,7 @@
     <t>Mobile app icon assets exist with exact required dimensions (1024x1024) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:44</t>
+    <t>2026-09-03 09:08:20</t>
   </si>
   <si>
     <t>DEP-TC-245</t>
@@ -3226,7 +3226,7 @@
     <t>Mobile adaptive icon background and foreground layers configured [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:54</t>
+    <t>2026-09-03 09:08:30</t>
   </si>
   <si>
     <t>DEP-TC-246</t>
@@ -3235,7 +3235,7 @@
     <t>Expo splash screen configuration with backgroundColor #1E1B4B [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:04</t>
+    <t>2026-09-03 09:08:40</t>
   </si>
   <si>
     <t>DEP-TC-247</t>
@@ -3244,7 +3244,7 @@
     <t>Mobile permissions declarations in app.json (Camera, Audio, Notifications) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:14</t>
+    <t>2026-09-03 09:08:50</t>
   </si>
   <si>
     <t>DEP-TC-248</t>
@@ -3253,7 +3253,7 @@
     <t>Mobile deep linking scheme defined ("skillswap") [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:24</t>
+    <t>2026-09-03 09:09:00</t>
   </si>
   <si>
     <t>DEP-TC-249</t>
@@ -3262,7 +3262,7 @@
     <t>Service worker registers smoothly for offline static asset caching [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:34</t>
+    <t>2026-09-03 09:09:10</t>
   </si>
   <si>
     <t>DEP-TC-250</t>
@@ -3271,7 +3271,7 @@
     <t>Lighthouse PWA installability criteria checklist audit [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:44</t>
+    <t>2026-09-03 09:09:20</t>
   </si>
   <si>
     <t>DEP-TC-251</t>
@@ -3280,7 +3280,7 @@
     <t>SPA fallback: Rewrites /dashboard, /messages, /profile to index.html [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:54</t>
+    <t>2026-09-03 09:09:30</t>
   </si>
   <si>
     <t>DEP-TC-252</t>
@@ -3289,7 +3289,7 @@
     <t>Catch-all wildcard route renders NotFoundPage component [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:04</t>
+    <t>2026-09-03 09:09:40</t>
   </si>
   <si>
     <t>DEP-TC-253</t>
@@ -3298,7 +3298,7 @@
     <t>Deep nested route param parsing (/profile/:userId) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:14</t>
+    <t>2026-09-03 09:09:50</t>
   </si>
   <si>
     <t>DEP-TC-254</t>
@@ -3307,7 +3307,7 @@
     <t>Query parameters parsing (?tab=security&amp;action=reset) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:24</t>
+    <t>2026-09-03 09:10:00</t>
   </si>
   <si>
     <t>DEP-TC-255</t>
@@ -3316,7 +3316,7 @@
     <t>Browser history pushState and back/forward navigation support [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:34</t>
+    <t>2026-09-03 09:10:10</t>
   </si>
   <si>
     <t>DEP-TC-256</t>
@@ -3325,7 +3325,7 @@
     <t>Scroll restoration to top on route change [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:44</t>
+    <t>2026-09-03 09:10:20</t>
   </si>
   <si>
     <t>DEP-TC-257</t>
@@ -3334,7 +3334,7 @@
     <t>Route transition animations and micro-interaction smoothness [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:54</t>
+    <t>2026-09-03 09:10:30</t>
   </si>
   <si>
     <t>DEP-TC-258</t>
@@ -3343,7 +3343,7 @@
     <t>Protected routes guard checks auth state before rendering children [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:04</t>
+    <t>2026-09-03 09:10:40</t>
   </si>
   <si>
     <t>DEP-TC-259</t>
@@ -3352,7 +3352,7 @@
     <t>Dynamic page document.title update on route navigation [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:14</t>
+    <t>2026-09-03 09:10:50</t>
   </si>
   <si>
     <t>DEP-TC-260</t>
@@ -3361,7 +3361,7 @@
     <t>Favicon links dynamically load correctly on all subroutes [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:24</t>
+    <t>2026-09-03 09:11:00</t>
   </si>
   <si>
     <t>DEP-TC-261</t>
@@ -3370,7 +3370,7 @@
     <t>Composite index defined for searchUsers (category ASC, rating DESC) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:34</t>
+    <t>2026-09-03 09:11:10</t>
   </si>
   <si>
     <t>DEP-TC-262</t>
@@ -3379,7 +3379,7 @@
     <t>Composite index defined for messages (conversationId ASC, createdAt ASC) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:44</t>
+    <t>2026-09-03 09:11:20</t>
   </si>
   <si>
     <t>DEP-TC-263</t>
@@ -3388,7 +3388,7 @@
     <t>Composite index for sessions (participants ARRAY, startTime ASC) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:54</t>
+    <t>2026-09-03 09:11:30</t>
   </si>
   <si>
     <t>DEP-TC-264</t>
@@ -3397,7 +3397,7 @@
     <t>Query cursor limit pagination (limit: 20 per batch) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:04</t>
+    <t>2026-09-03 09:11:40</t>
   </si>
   <si>
     <t>DEP-TC-265</t>
@@ -3406,7 +3406,7 @@
     <t>Indexed queries execute with latency under 100ms in cloud region [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:14</t>
+    <t>2026-09-03 09:11:50</t>
   </si>
   <si>
     <t>DEP-TC-266</t>
@@ -3415,7 +3415,7 @@
     <t>Document write batch size within Firestore limits (&lt;500 writes per batch) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:24</t>
+    <t>2026-09-03 09:12:00</t>
   </si>
   <si>
     <t>DEP-TC-267</t>
@@ -3424,7 +3424,7 @@
     <t>Firestore offline persistence enabled for IndexedDB storage [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:34</t>
+    <t>2026-09-03 09:12:10</t>
   </si>
   <si>
     <t>DEP-TC-268</t>
@@ -3433,7 +3433,7 @@
     <t>Collection group query for public reviews across all users [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:44</t>
+    <t>2026-09-03 09:12:20</t>
   </si>
   <si>
     <t>DEP-TC-269</t>
@@ -3442,7 +3442,7 @@
     <t>Document fields count within limits (&lt;20,000 fields per document) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:54</t>
+    <t>2026-09-03 09:12:30</t>
   </si>
   <si>
     <t>DEP-TC-270</t>
@@ -3451,7 +3451,7 @@
     <t>Data backup and export automation readiness [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:04</t>
+    <t>2026-09-03 09:12:40</t>
   </si>
   <si>
     <t>DEP-TC-271</t>
@@ -3460,7 +3460,7 @@
     <t>Largest Contentful Paint (LCP) benchmark under 2.5 seconds [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:14</t>
+    <t>2026-09-03 09:12:50</t>
   </si>
   <si>
     <t>DEP-TC-272</t>
@@ -3469,7 +3469,7 @@
     <t>First Input Delay (FID) / INP benchmark under 100 milliseconds [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:24</t>
+    <t>2026-09-03 09:13:00</t>
   </si>
   <si>
     <t>DEP-TC-273</t>
@@ -3478,7 +3478,7 @@
     <t>Cumulative Layout Shift (CLS) score under 0.1 [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:34</t>
+    <t>2026-09-03 09:13:10</t>
   </si>
   <si>
     <t>DEP-TC-274</t>
@@ -3487,7 +3487,7 @@
     <t>First Contentful Paint (FCP) benchmark under 1.2 seconds [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:44</t>
+    <t>2026-09-03 09:13:20</t>
   </si>
   <si>
     <t>DEP-TC-275</t>
@@ -3496,7 +3496,7 @@
     <t>Time to Interactive (TTI) benchmark under 2.0 seconds [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:54</t>
+    <t>2026-09-03 09:13:30</t>
   </si>
   <si>
     <t>DEP-TC-276</t>
@@ -3505,7 +3505,7 @@
     <t>Total Blocking Time (TBT) benchmark under 150 milliseconds [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:04</t>
+    <t>2026-09-03 09:13:40</t>
   </si>
   <si>
     <t>DEP-TC-277</t>
@@ -3514,7 +3514,7 @@
     <t>Font preloading with swap display (font-display: swap) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:14</t>
+    <t>2026-09-03 09:13:50</t>
   </si>
   <si>
     <t>DEP-TC-278</t>
@@ -3523,7 +3523,7 @@
     <t>Image lazy loading with loading="lazy" attribute [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:24</t>
+    <t>2026-09-03 09:14:00</t>
   </si>
   <si>
     <t>DEP-TC-279</t>
@@ -3532,7 +3532,7 @@
     <t>Gzip / Brotli compression enabled on web server [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:34</t>
+    <t>2026-09-03 09:14:10</t>
   </si>
   <si>
     <t>DEP-TC-280</t>
@@ -3541,7 +3541,7 @@
     <t>Static asset Cache-Control headers (max-age=31536000, immutable) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:44</t>
+    <t>2026-09-03 09:14:20</t>
   </si>
   <si>
     <t>DEP-TC-281</t>
@@ -3550,7 +3550,7 @@
     <t>Color contrast ratio meets WCAG AA standard (Minimum 4.5:1 for text) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:54</t>
+    <t>2026-09-03 09:14:30</t>
   </si>
   <si>
     <t>DEP-TC-282</t>
@@ -3559,7 +3559,7 @@
     <t>All interactive elements have accessible aria-label or visible text [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:04</t>
+    <t>2026-09-03 09:14:40</t>
   </si>
   <si>
     <t>DEP-TC-283</t>
@@ -3568,7 +3568,7 @@
     <t>Keyboard navigation focus rings visible on all clickable elements [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:14</t>
+    <t>2026-09-03 09:14:50</t>
   </si>
   <si>
     <t>DEP-TC-284</t>
@@ -3577,7 +3577,7 @@
     <t>Semantic HTML5 landmark elements used (&lt;header&gt;, &lt;nav&gt;, &lt;main&gt;, &lt;aside&gt;) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:24</t>
+    <t>2026-09-03 09:15:00</t>
   </si>
   <si>
     <t>DEP-TC-285</t>
@@ -3586,7 +3586,7 @@
     <t>Single &lt;h1&gt; tag per page with structured &lt;h2&gt; and &lt;h3&gt; hierarchy [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:34</t>
+    <t>2026-09-03 09:15:10</t>
   </si>
   <si>
     <t>DEP-TC-286</t>
@@ -3595,7 +3595,7 @@
     <t>All images have descriptive alt attributes [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:44</t>
+    <t>2026-09-03 09:15:20</t>
   </si>
   <si>
     <t>DEP-TC-287</t>
@@ -3604,7 +3604,7 @@
     <t>Form inputs have associated &lt;label&gt; elements with htmlFor matching id [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:54</t>
+    <t>2026-09-03 09:15:30</t>
   </si>
   <si>
     <t>DEP-TC-288</t>
@@ -3613,7 +3613,7 @@
     <t>Screen reader announcement for dynamic live updates (aria-live="polite") [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:04</t>
+    <t>2026-09-03 09:15:40</t>
   </si>
   <si>
     <t>DEP-TC-289</t>
@@ -3622,7 +3622,7 @@
     <t>Open Graph meta tags (og:title, og:description, og:image) for link sharing [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:14</t>
+    <t>2026-09-03 09:15:50</t>
   </si>
   <si>
     <t>DEP-TC-290</t>
@@ -3631,7 +3631,7 @@
     <t>Valid robots.txt and sitemap.xml configuration [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:24</t>
+    <t>2026-09-03 09:16:00</t>
   </si>
   <si>
     <t>DEP-TC-291</t>
@@ -3640,7 +3640,7 @@
     <t>GitHub Actions workflow triggers on push to main branch [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:34</t>
+    <t>2026-09-03 09:16:10</t>
   </si>
   <si>
     <t>DEP-TC-292</t>
@@ -3649,7 +3649,7 @@
     <t>GitHub Actions workflow triggers on pull request creation [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:44</t>
+    <t>2026-09-03 09:16:20</t>
   </si>
   <si>
     <t>DEP-TC-293</t>
@@ -3658,7 +3658,7 @@
     <t>Multi-job parallel matrix execution (Ubuntu, Node 20) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:54</t>
+    <t>2026-09-03 09:16:30</t>
   </si>
   <si>
     <t>DEP-TC-294</t>
@@ -3667,7 +3667,7 @@
     <t>Automated artifact upload for individual test reports (.xlsx) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:04</t>
+    <t>2026-09-03 09:16:40</t>
   </si>
   <si>
     <t>DEP-TC-295</t>
@@ -3676,7 +3676,7 @@
     <t>Master consolidated Excel report compilation job [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:14</t>
+    <t>2026-09-03 09:16:50</t>
   </si>
   <si>
     <t>DEP-TC-296</t>
@@ -3685,7 +3685,7 @@
     <t>Publish test summary table to GitHub Actions job summary ($GITHUB_STEP_SUMMARY) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:24</t>
+    <t>2026-09-03 09:17:00</t>
   </si>
   <si>
     <t>DEP-TC-297</t>
@@ -3694,7 +3694,7 @@
     <t>Automated deployment to Firebase Hosting / Vercel upon all tests passing [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:34</t>
+    <t>2026-09-03 09:17:10</t>
   </si>
   <si>
     <t>DEP-TC-298</t>
@@ -3703,7 +3703,7 @@
     <t>Discord / Slack notification webhook on build failure or success [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:44</t>
+    <t>2026-09-03 09:17:20</t>
   </si>
   <si>
     <t>DEP-TC-299</t>
@@ -3712,7 +3712,7 @@
     <t>Security vulnerability dependency scanner step (npm audit) [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:54</t>
+    <t>2026-09-03 09:17:30</t>
   </si>
   <si>
     <t>DEP-TC-300</t>
@@ -3721,7 +3721,7 @@
     <t>Automated semantic release tag and changelog generation [Security &amp; Compliance Hardening Audit]</t>
   </si>
   <si>
-    <t>2026-09-03 09:10:04</t>
+    <t>2026-09-03 09:17:40</t>
   </si>
 </sst>
 </file>
@@ -4263,7 +4263,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4304,7 +4304,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>22</v>
@@ -4345,7 +4345,7 @@
         <v>36</v>
       </c>
       <c r="J4" s="2">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>22</v>
@@ -4386,7 +4386,7 @@
         <v>43</v>
       </c>
       <c r="J5" s="5">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>22</v>
@@ -4427,7 +4427,7 @@
         <v>49</v>
       </c>
       <c r="J6" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>22</v>
@@ -4468,7 +4468,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="5">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>22</v>
@@ -4509,7 +4509,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>22</v>
@@ -4550,7 +4550,7 @@
         <v>67</v>
       </c>
       <c r="J9" s="5">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>22</v>
@@ -4591,7 +4591,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>22</v>
@@ -4632,7 +4632,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>22</v>
@@ -4673,7 +4673,7 @@
         <v>87</v>
       </c>
       <c r="J12" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>22</v>
@@ -4714,7 +4714,7 @@
         <v>93</v>
       </c>
       <c r="J13" s="5">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>22</v>
@@ -4755,7 +4755,7 @@
         <v>99</v>
       </c>
       <c r="J14" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>22</v>
@@ -4796,7 +4796,7 @@
         <v>105</v>
       </c>
       <c r="J15" s="5">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>22</v>
@@ -4837,7 +4837,7 @@
         <v>111</v>
       </c>
       <c r="J16" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>22</v>
@@ -4878,7 +4878,7 @@
         <v>117</v>
       </c>
       <c r="J17" s="5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>22</v>
@@ -4919,7 +4919,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>22</v>
@@ -4960,7 +4960,7 @@
         <v>129</v>
       </c>
       <c r="J19" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>22</v>
@@ -5001,7 +5001,7 @@
         <v>135</v>
       </c>
       <c r="J20" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>22</v>
@@ -5042,7 +5042,7 @@
         <v>141</v>
       </c>
       <c r="J21" s="5">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>22</v>
@@ -5083,7 +5083,7 @@
         <v>149</v>
       </c>
       <c r="J22" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>22</v>
@@ -5165,7 +5165,7 @@
         <v>161</v>
       </c>
       <c r="J24" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>22</v>
@@ -5206,7 +5206,7 @@
         <v>167</v>
       </c>
       <c r="J25" s="5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>22</v>
@@ -5247,7 +5247,7 @@
         <v>173</v>
       </c>
       <c r="J26" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>22</v>
@@ -5288,7 +5288,7 @@
         <v>179</v>
       </c>
       <c r="J27" s="5">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>22</v>
@@ -5329,7 +5329,7 @@
         <v>185</v>
       </c>
       <c r="J28" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>22</v>
@@ -5370,7 +5370,7 @@
         <v>191</v>
       </c>
       <c r="J29" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>22</v>
@@ -5411,7 +5411,7 @@
         <v>197</v>
       </c>
       <c r="J30" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>22</v>
@@ -5452,7 +5452,7 @@
         <v>203</v>
       </c>
       <c r="J31" s="5">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>22</v>
@@ -5493,7 +5493,7 @@
         <v>211</v>
       </c>
       <c r="J32" s="2">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>22</v>
@@ -5534,7 +5534,7 @@
         <v>217</v>
       </c>
       <c r="J33" s="5">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>22</v>
@@ -5575,7 +5575,7 @@
         <v>223</v>
       </c>
       <c r="J34" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>22</v>
@@ -5616,7 +5616,7 @@
         <v>229</v>
       </c>
       <c r="J35" s="5">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>22</v>
@@ -5657,7 +5657,7 @@
         <v>235</v>
       </c>
       <c r="J36" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>22</v>
@@ -5698,7 +5698,7 @@
         <v>241</v>
       </c>
       <c r="J37" s="5">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>22</v>
@@ -5780,7 +5780,7 @@
         <v>253</v>
       </c>
       <c r="J39" s="5">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -5821,7 +5821,7 @@
         <v>259</v>
       </c>
       <c r="J40" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>22</v>
@@ -5862,7 +5862,7 @@
         <v>265</v>
       </c>
       <c r="J41" s="5">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>22</v>
@@ -5903,7 +5903,7 @@
         <v>273</v>
       </c>
       <c r="J42" s="2">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>22</v>
@@ -5944,7 +5944,7 @@
         <v>279</v>
       </c>
       <c r="J43" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>22</v>
@@ -5985,7 +5985,7 @@
         <v>279</v>
       </c>
       <c r="J44" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>22</v>
@@ -6026,7 +6026,7 @@
         <v>289</v>
       </c>
       <c r="J45" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>22</v>
@@ -6067,7 +6067,7 @@
         <v>295</v>
       </c>
       <c r="J46" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>22</v>
@@ -6108,7 +6108,7 @@
         <v>301</v>
       </c>
       <c r="J47" s="5">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>22</v>
@@ -6149,7 +6149,7 @@
         <v>307</v>
       </c>
       <c r="J48" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>22</v>
@@ -6190,7 +6190,7 @@
         <v>313</v>
       </c>
       <c r="J49" s="5">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>22</v>
@@ -6231,7 +6231,7 @@
         <v>319</v>
       </c>
       <c r="J50" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>22</v>
@@ -6272,7 +6272,7 @@
         <v>325</v>
       </c>
       <c r="J51" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>22</v>
@@ -6354,7 +6354,7 @@
         <v>339</v>
       </c>
       <c r="J53" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>22</v>
@@ -6395,7 +6395,7 @@
         <v>345</v>
       </c>
       <c r="J54" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>22</v>
@@ -6436,7 +6436,7 @@
         <v>351</v>
       </c>
       <c r="J55" s="5">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>22</v>
@@ -6477,7 +6477,7 @@
         <v>357</v>
       </c>
       <c r="J56" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>22</v>
@@ -6518,7 +6518,7 @@
         <v>363</v>
       </c>
       <c r="J57" s="5">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>22</v>
@@ -6559,7 +6559,7 @@
         <v>369</v>
       </c>
       <c r="J58" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>22</v>
@@ -6600,7 +6600,7 @@
         <v>375</v>
       </c>
       <c r="J59" s="5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>22</v>
@@ -6641,7 +6641,7 @@
         <v>381</v>
       </c>
       <c r="J60" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>22</v>
@@ -6682,7 +6682,7 @@
         <v>387</v>
       </c>
       <c r="J61" s="5">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>22</v>
@@ -6723,7 +6723,7 @@
         <v>395</v>
       </c>
       <c r="J62" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>22</v>
@@ -6764,7 +6764,7 @@
         <v>401</v>
       </c>
       <c r="J63" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>22</v>
@@ -6805,7 +6805,7 @@
         <v>407</v>
       </c>
       <c r="J64" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>22</v>
@@ -6846,7 +6846,7 @@
         <v>413</v>
       </c>
       <c r="J65" s="5">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>22</v>
@@ -6887,7 +6887,7 @@
         <v>419</v>
       </c>
       <c r="J66" s="2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>22</v>
@@ -6928,7 +6928,7 @@
         <v>425</v>
       </c>
       <c r="J67" s="5">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>22</v>
@@ -6969,7 +6969,7 @@
         <v>431</v>
       </c>
       <c r="J68" s="2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>22</v>
@@ -7010,7 +7010,7 @@
         <v>437</v>
       </c>
       <c r="J69" s="5">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>22</v>
@@ -7051,7 +7051,7 @@
         <v>443</v>
       </c>
       <c r="J70" s="2">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>22</v>
@@ -7092,7 +7092,7 @@
         <v>449</v>
       </c>
       <c r="J71" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>22</v>
@@ -7133,7 +7133,7 @@
         <v>457</v>
       </c>
       <c r="J72" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>22</v>
@@ -7174,7 +7174,7 @@
         <v>463</v>
       </c>
       <c r="J73" s="5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>22</v>
@@ -7215,7 +7215,7 @@
         <v>469</v>
       </c>
       <c r="J74" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>22</v>
@@ -7256,7 +7256,7 @@
         <v>475</v>
       </c>
       <c r="J75" s="5">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>22</v>
@@ -7297,7 +7297,7 @@
         <v>481</v>
       </c>
       <c r="J76" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>22</v>
@@ -7338,7 +7338,7 @@
         <v>487</v>
       </c>
       <c r="J77" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>22</v>
@@ -7379,7 +7379,7 @@
         <v>493</v>
       </c>
       <c r="J78" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>22</v>
@@ -7420,7 +7420,7 @@
         <v>499</v>
       </c>
       <c r="J79" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>22</v>
@@ -7461,7 +7461,7 @@
         <v>505</v>
       </c>
       <c r="J80" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>22</v>
@@ -7502,7 +7502,7 @@
         <v>511</v>
       </c>
       <c r="J81" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>22</v>
@@ -7543,7 +7543,7 @@
         <v>519</v>
       </c>
       <c r="J82" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>22</v>
@@ -7584,7 +7584,7 @@
         <v>525</v>
       </c>
       <c r="J83" s="5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>22</v>
@@ -7625,7 +7625,7 @@
         <v>531</v>
       </c>
       <c r="J84" s="2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>22</v>
@@ -7666,7 +7666,7 @@
         <v>537</v>
       </c>
       <c r="J85" s="5">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>22</v>
@@ -7748,7 +7748,7 @@
         <v>549</v>
       </c>
       <c r="J87" s="5">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>22</v>
@@ -7789,7 +7789,7 @@
         <v>555</v>
       </c>
       <c r="J88" s="2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>22</v>
@@ -7830,7 +7830,7 @@
         <v>561</v>
       </c>
       <c r="J89" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>22</v>
@@ -7912,7 +7912,7 @@
         <v>573</v>
       </c>
       <c r="J91" s="5">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>22</v>
@@ -7953,7 +7953,7 @@
         <v>581</v>
       </c>
       <c r="J92" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>22</v>
@@ -7994,7 +7994,7 @@
         <v>587</v>
       </c>
       <c r="J93" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>22</v>
@@ -8035,7 +8035,7 @@
         <v>593</v>
       </c>
       <c r="J94" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>22</v>
@@ -8076,7 +8076,7 @@
         <v>599</v>
       </c>
       <c r="J95" s="5">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>22</v>
@@ -8117,7 +8117,7 @@
         <v>605</v>
       </c>
       <c r="J96" s="2">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>22</v>
@@ -8158,7 +8158,7 @@
         <v>611</v>
       </c>
       <c r="J97" s="5">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>22</v>
@@ -8199,7 +8199,7 @@
         <v>617</v>
       </c>
       <c r="J98" s="2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>22</v>
@@ -8240,7 +8240,7 @@
         <v>623</v>
       </c>
       <c r="J99" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>22</v>
@@ -8281,7 +8281,7 @@
         <v>629</v>
       </c>
       <c r="J100" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>22</v>
@@ -8322,7 +8322,7 @@
         <v>635</v>
       </c>
       <c r="J101" s="5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>22</v>
@@ -8363,7 +8363,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>22</v>
@@ -8404,7 +8404,7 @@
         <v>29</v>
       </c>
       <c r="J103" s="5">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>22</v>
@@ -8445,7 +8445,7 @@
         <v>36</v>
       </c>
       <c r="J104" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>22</v>
@@ -8486,7 +8486,7 @@
         <v>43</v>
       </c>
       <c r="J105" s="5">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>22</v>
@@ -8527,7 +8527,7 @@
         <v>49</v>
       </c>
       <c r="J106" s="2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>22</v>
@@ -8568,7 +8568,7 @@
         <v>55</v>
       </c>
       <c r="J107" s="5">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>22</v>
@@ -8609,7 +8609,7 @@
         <v>61</v>
       </c>
       <c r="J108" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>22</v>
@@ -8650,7 +8650,7 @@
         <v>67</v>
       </c>
       <c r="J109" s="5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>22</v>
@@ -8691,7 +8691,7 @@
         <v>73</v>
       </c>
       <c r="J110" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>22</v>
@@ -8732,7 +8732,7 @@
         <v>79</v>
       </c>
       <c r="J111" s="5">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>22</v>
@@ -8773,7 +8773,7 @@
         <v>87</v>
       </c>
       <c r="J112" s="2">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>22</v>
@@ -8814,7 +8814,7 @@
         <v>93</v>
       </c>
       <c r="J113" s="5">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>22</v>
@@ -8855,7 +8855,7 @@
         <v>99</v>
       </c>
       <c r="J114" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>22</v>
@@ -8896,7 +8896,7 @@
         <v>105</v>
       </c>
       <c r="J115" s="5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>22</v>
@@ -8937,7 +8937,7 @@
         <v>111</v>
       </c>
       <c r="J116" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>22</v>
@@ -8978,7 +8978,7 @@
         <v>117</v>
       </c>
       <c r="J117" s="5">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>22</v>
@@ -9019,7 +9019,7 @@
         <v>123</v>
       </c>
       <c r="J118" s="2">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>22</v>
@@ -9060,7 +9060,7 @@
         <v>129</v>
       </c>
       <c r="J119" s="5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>22</v>
@@ -9101,7 +9101,7 @@
         <v>135</v>
       </c>
       <c r="J120" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>22</v>
@@ -9142,7 +9142,7 @@
         <v>141</v>
       </c>
       <c r="J121" s="5">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>22</v>
@@ -9183,7 +9183,7 @@
         <v>149</v>
       </c>
       <c r="J122" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>22</v>
@@ -9265,7 +9265,7 @@
         <v>161</v>
       </c>
       <c r="J124" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>22</v>
@@ -9306,7 +9306,7 @@
         <v>167</v>
       </c>
       <c r="J125" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>22</v>
@@ -9347,7 +9347,7 @@
         <v>173</v>
       </c>
       <c r="J126" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>22</v>
@@ -9388,7 +9388,7 @@
         <v>179</v>
       </c>
       <c r="J127" s="5">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>22</v>
@@ -9429,7 +9429,7 @@
         <v>185</v>
       </c>
       <c r="J128" s="2">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>22</v>
@@ -9470,7 +9470,7 @@
         <v>191</v>
       </c>
       <c r="J129" s="5">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>22</v>
@@ -9511,7 +9511,7 @@
         <v>197</v>
       </c>
       <c r="J130" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>22</v>
@@ -9552,7 +9552,7 @@
         <v>203</v>
       </c>
       <c r="J131" s="5">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>22</v>
@@ -9593,7 +9593,7 @@
         <v>211</v>
       </c>
       <c r="J132" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>22</v>
@@ -9634,7 +9634,7 @@
         <v>217</v>
       </c>
       <c r="J133" s="5">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>22</v>
@@ -9675,7 +9675,7 @@
         <v>223</v>
       </c>
       <c r="J134" s="2">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>22</v>
@@ -9716,7 +9716,7 @@
         <v>229</v>
       </c>
       <c r="J135" s="5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>22</v>
@@ -9757,7 +9757,7 @@
         <v>235</v>
       </c>
       <c r="J136" s="2">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>22</v>
@@ -9798,7 +9798,7 @@
         <v>241</v>
       </c>
       <c r="J137" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>22</v>
@@ -9839,7 +9839,7 @@
         <v>247</v>
       </c>
       <c r="J138" s="2">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>22</v>
@@ -9880,7 +9880,7 @@
         <v>253</v>
       </c>
       <c r="J139" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>22</v>
@@ -9921,7 +9921,7 @@
         <v>259</v>
       </c>
       <c r="J140" s="2">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>22</v>
@@ -9962,7 +9962,7 @@
         <v>265</v>
       </c>
       <c r="J141" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>22</v>
@@ -10003,7 +10003,7 @@
         <v>273</v>
       </c>
       <c r="J142" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>22</v>
@@ -10044,7 +10044,7 @@
         <v>279</v>
       </c>
       <c r="J143" s="5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>22</v>
@@ -10085,7 +10085,7 @@
         <v>279</v>
       </c>
       <c r="J144" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>22</v>
@@ -10126,7 +10126,7 @@
         <v>289</v>
       </c>
       <c r="J145" s="5">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>22</v>
@@ -10208,7 +10208,7 @@
         <v>301</v>
       </c>
       <c r="J147" s="5">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>22</v>
@@ -10249,7 +10249,7 @@
         <v>307</v>
       </c>
       <c r="J148" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>22</v>
@@ -10290,7 +10290,7 @@
         <v>313</v>
       </c>
       <c r="J149" s="5">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>22</v>
@@ -10331,7 +10331,7 @@
         <v>319</v>
       </c>
       <c r="J150" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>22</v>
@@ -10372,7 +10372,7 @@
         <v>325</v>
       </c>
       <c r="J151" s="5">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>22</v>
@@ -10413,7 +10413,7 @@
         <v>333</v>
       </c>
       <c r="J152" s="2">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>22</v>
@@ -10454,7 +10454,7 @@
         <v>339</v>
       </c>
       <c r="J153" s="5">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>22</v>
@@ -10495,7 +10495,7 @@
         <v>345</v>
       </c>
       <c r="J154" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>22</v>
@@ -10536,7 +10536,7 @@
         <v>351</v>
       </c>
       <c r="J155" s="5">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>22</v>
@@ -10577,7 +10577,7 @@
         <v>357</v>
       </c>
       <c r="J156" s="2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>22</v>
@@ -10618,7 +10618,7 @@
         <v>363</v>
       </c>
       <c r="J157" s="5">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>22</v>
@@ -10659,7 +10659,7 @@
         <v>369</v>
       </c>
       <c r="J158" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>22</v>
@@ -10700,7 +10700,7 @@
         <v>375</v>
       </c>
       <c r="J159" s="5">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>22</v>
@@ -10741,7 +10741,7 @@
         <v>381</v>
       </c>
       <c r="J160" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>22</v>
@@ -10782,7 +10782,7 @@
         <v>387</v>
       </c>
       <c r="J161" s="5">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>22</v>
@@ -10823,7 +10823,7 @@
         <v>395</v>
       </c>
       <c r="J162" s="2">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>22</v>
@@ -10864,7 +10864,7 @@
         <v>401</v>
       </c>
       <c r="J163" s="5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>22</v>
@@ -10905,7 +10905,7 @@
         <v>407</v>
       </c>
       <c r="J164" s="2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>22</v>
@@ -10946,7 +10946,7 @@
         <v>413</v>
       </c>
       <c r="J165" s="5">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>22</v>
@@ -10987,7 +10987,7 @@
         <v>419</v>
       </c>
       <c r="J166" s="2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>22</v>
@@ -11028,7 +11028,7 @@
         <v>425</v>
       </c>
       <c r="J167" s="5">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>22</v>
@@ -11069,7 +11069,7 @@
         <v>431</v>
       </c>
       <c r="J168" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>22</v>
@@ -11110,7 +11110,7 @@
         <v>437</v>
       </c>
       <c r="J169" s="5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>22</v>
@@ -11151,7 +11151,7 @@
         <v>443</v>
       </c>
       <c r="J170" s="2">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>22</v>
@@ -11192,7 +11192,7 @@
         <v>449</v>
       </c>
       <c r="J171" s="5">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>22</v>
@@ -11233,7 +11233,7 @@
         <v>457</v>
       </c>
       <c r="J172" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>22</v>
@@ -11274,7 +11274,7 @@
         <v>463</v>
       </c>
       <c r="J173" s="5">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>22</v>
@@ -11315,7 +11315,7 @@
         <v>469</v>
       </c>
       <c r="J174" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>22</v>
@@ -11356,7 +11356,7 @@
         <v>475</v>
       </c>
       <c r="J175" s="5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>22</v>
@@ -11397,7 +11397,7 @@
         <v>481</v>
       </c>
       <c r="J176" s="2">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>22</v>
@@ -11438,7 +11438,7 @@
         <v>487</v>
       </c>
       <c r="J177" s="5">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>22</v>
@@ -11479,7 +11479,7 @@
         <v>493</v>
       </c>
       <c r="J178" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>22</v>
@@ -11520,7 +11520,7 @@
         <v>499</v>
       </c>
       <c r="J179" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>22</v>
@@ -11561,7 +11561,7 @@
         <v>505</v>
       </c>
       <c r="J180" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>22</v>
@@ -11602,7 +11602,7 @@
         <v>511</v>
       </c>
       <c r="J181" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>22</v>
@@ -11643,7 +11643,7 @@
         <v>519</v>
       </c>
       <c r="J182" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>22</v>
@@ -11684,7 +11684,7 @@
         <v>525</v>
       </c>
       <c r="J183" s="5">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>22</v>
@@ -11725,7 +11725,7 @@
         <v>531</v>
       </c>
       <c r="J184" s="2">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>22</v>
@@ -11766,7 +11766,7 @@
         <v>537</v>
       </c>
       <c r="J185" s="5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>22</v>
@@ -11889,7 +11889,7 @@
         <v>555</v>
       </c>
       <c r="J188" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>22</v>
@@ -11930,7 +11930,7 @@
         <v>561</v>
       </c>
       <c r="J189" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>22</v>
@@ -11971,7 +11971,7 @@
         <v>567</v>
       </c>
       <c r="J190" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>22</v>
@@ -12012,7 +12012,7 @@
         <v>573</v>
       </c>
       <c r="J191" s="5">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>22</v>
@@ -12053,7 +12053,7 @@
         <v>581</v>
       </c>
       <c r="J192" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>22</v>
@@ -12094,7 +12094,7 @@
         <v>587</v>
       </c>
       <c r="J193" s="5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>22</v>
@@ -12135,7 +12135,7 @@
         <v>593</v>
       </c>
       <c r="J194" s="2">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K194" s="4" t="s">
         <v>22</v>
@@ -12176,7 +12176,7 @@
         <v>599</v>
       </c>
       <c r="J195" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>22</v>
@@ -12217,7 +12217,7 @@
         <v>605</v>
       </c>
       <c r="J196" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>22</v>
@@ -12258,7 +12258,7 @@
         <v>611</v>
       </c>
       <c r="J197" s="5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>22</v>
@@ -12299,7 +12299,7 @@
         <v>617</v>
       </c>
       <c r="J198" s="2">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>22</v>
@@ -12340,7 +12340,7 @@
         <v>623</v>
       </c>
       <c r="J199" s="5">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>22</v>
@@ -12381,7 +12381,7 @@
         <v>629</v>
       </c>
       <c r="J200" s="2">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>22</v>
@@ -12422,7 +12422,7 @@
         <v>635</v>
       </c>
       <c r="J201" s="5">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>22</v>
@@ -12463,7 +12463,7 @@
         <v>21</v>
       </c>
       <c r="J202" s="2">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>22</v>
@@ -12504,7 +12504,7 @@
         <v>29</v>
       </c>
       <c r="J203" s="5">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>22</v>
@@ -12545,7 +12545,7 @@
         <v>36</v>
       </c>
       <c r="J204" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>22</v>
@@ -12586,7 +12586,7 @@
         <v>43</v>
       </c>
       <c r="J205" s="5">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K205" s="4" t="s">
         <v>22</v>
@@ -12627,7 +12627,7 @@
         <v>49</v>
       </c>
       <c r="J206" s="2">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>22</v>
@@ -12668,7 +12668,7 @@
         <v>55</v>
       </c>
       <c r="J207" s="5">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>22</v>
@@ -12709,7 +12709,7 @@
         <v>61</v>
       </c>
       <c r="J208" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>22</v>
@@ -12750,7 +12750,7 @@
         <v>67</v>
       </c>
       <c r="J209" s="5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>22</v>
@@ -12791,7 +12791,7 @@
         <v>73</v>
       </c>
       <c r="J210" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>22</v>
@@ -12832,7 +12832,7 @@
         <v>79</v>
       </c>
       <c r="J211" s="5">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>22</v>
@@ -12873,7 +12873,7 @@
         <v>87</v>
       </c>
       <c r="J212" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>22</v>
@@ -12996,7 +12996,7 @@
         <v>105</v>
       </c>
       <c r="J215" s="5">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>22</v>
@@ -13037,7 +13037,7 @@
         <v>111</v>
       </c>
       <c r="J216" s="2">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>22</v>
@@ -13078,7 +13078,7 @@
         <v>117</v>
       </c>
       <c r="J217" s="5">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>22</v>
@@ -13119,7 +13119,7 @@
         <v>123</v>
       </c>
       <c r="J218" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K218" s="4" t="s">
         <v>22</v>
@@ -13160,7 +13160,7 @@
         <v>129</v>
       </c>
       <c r="J219" s="5">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>22</v>
@@ -13201,7 +13201,7 @@
         <v>135</v>
       </c>
       <c r="J220" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>22</v>
@@ -13242,7 +13242,7 @@
         <v>141</v>
       </c>
       <c r="J221" s="5">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>22</v>
@@ -13283,7 +13283,7 @@
         <v>149</v>
       </c>
       <c r="J222" s="2">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>22</v>
@@ -13324,7 +13324,7 @@
         <v>155</v>
       </c>
       <c r="J223" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>22</v>
@@ -13365,7 +13365,7 @@
         <v>161</v>
       </c>
       <c r="J224" s="2">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>22</v>
@@ -13406,7 +13406,7 @@
         <v>167</v>
       </c>
       <c r="J225" s="5">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>22</v>
@@ -13447,7 +13447,7 @@
         <v>173</v>
       </c>
       <c r="J226" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>22</v>
@@ -13488,7 +13488,7 @@
         <v>179</v>
       </c>
       <c r="J227" s="5">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>22</v>
@@ -13529,7 +13529,7 @@
         <v>185</v>
       </c>
       <c r="J228" s="2">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>22</v>
@@ -13611,7 +13611,7 @@
         <v>197</v>
       </c>
       <c r="J230" s="2">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>22</v>
@@ -13652,7 +13652,7 @@
         <v>203</v>
       </c>
       <c r="J231" s="5">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>22</v>
@@ -13693,7 +13693,7 @@
         <v>211</v>
       </c>
       <c r="J232" s="2">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>22</v>
@@ -13734,7 +13734,7 @@
         <v>217</v>
       </c>
       <c r="J233" s="5">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>22</v>
@@ -13775,7 +13775,7 @@
         <v>223</v>
       </c>
       <c r="J234" s="2">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>22</v>
@@ -13816,7 +13816,7 @@
         <v>229</v>
       </c>
       <c r="J235" s="5">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>22</v>
@@ -13857,7 +13857,7 @@
         <v>235</v>
       </c>
       <c r="J236" s="2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K236" s="4" t="s">
         <v>22</v>
@@ -13939,7 +13939,7 @@
         <v>247</v>
       </c>
       <c r="J238" s="2">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>22</v>
@@ -13980,7 +13980,7 @@
         <v>253</v>
       </c>
       <c r="J239" s="5">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>22</v>
@@ -14021,7 +14021,7 @@
         <v>259</v>
       </c>
       <c r="J240" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>22</v>
@@ -14062,7 +14062,7 @@
         <v>265</v>
       </c>
       <c r="J241" s="5">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K241" s="4" t="s">
         <v>22</v>
@@ -14103,7 +14103,7 @@
         <v>273</v>
       </c>
       <c r="J242" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>22</v>
@@ -14144,7 +14144,7 @@
         <v>279</v>
       </c>
       <c r="J243" s="5">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>22</v>
@@ -14185,7 +14185,7 @@
         <v>279</v>
       </c>
       <c r="J244" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>22</v>
@@ -14226,7 +14226,7 @@
         <v>289</v>
       </c>
       <c r="J245" s="5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>22</v>
@@ -14267,7 +14267,7 @@
         <v>295</v>
       </c>
       <c r="J246" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>22</v>
@@ -14308,7 +14308,7 @@
         <v>301</v>
       </c>
       <c r="J247" s="5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>22</v>
@@ -14349,7 +14349,7 @@
         <v>307</v>
       </c>
       <c r="J248" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>22</v>
@@ -14390,7 +14390,7 @@
         <v>313</v>
       </c>
       <c r="J249" s="5">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>22</v>
@@ -14431,7 +14431,7 @@
         <v>319</v>
       </c>
       <c r="J250" s="2">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>22</v>
@@ -14472,7 +14472,7 @@
         <v>325</v>
       </c>
       <c r="J251" s="5">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>22</v>
@@ -14513,7 +14513,7 @@
         <v>333</v>
       </c>
       <c r="J252" s="2">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>22</v>
@@ -14554,7 +14554,7 @@
         <v>339</v>
       </c>
       <c r="J253" s="5">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>22</v>
@@ -14595,7 +14595,7 @@
         <v>345</v>
       </c>
       <c r="J254" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>22</v>
@@ -14636,7 +14636,7 @@
         <v>351</v>
       </c>
       <c r="J255" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>22</v>
@@ -14677,7 +14677,7 @@
         <v>357</v>
       </c>
       <c r="J256" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>22</v>
@@ -14759,7 +14759,7 @@
         <v>369</v>
       </c>
       <c r="J258" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>22</v>
@@ -14800,7 +14800,7 @@
         <v>375</v>
       </c>
       <c r="J259" s="5">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>22</v>
@@ -14841,7 +14841,7 @@
         <v>381</v>
       </c>
       <c r="J260" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>22</v>
@@ -14882,7 +14882,7 @@
         <v>387</v>
       </c>
       <c r="J261" s="5">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>22</v>
@@ -14923,7 +14923,7 @@
         <v>395</v>
       </c>
       <c r="J262" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>22</v>
@@ -14964,7 +14964,7 @@
         <v>401</v>
       </c>
       <c r="J263" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>22</v>
@@ -15005,7 +15005,7 @@
         <v>407</v>
       </c>
       <c r="J264" s="2">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>22</v>
@@ -15046,7 +15046,7 @@
         <v>413</v>
       </c>
       <c r="J265" s="5">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="K265" s="4" t="s">
         <v>22</v>
@@ -15087,7 +15087,7 @@
         <v>419</v>
       </c>
       <c r="J266" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>22</v>
@@ -15128,7 +15128,7 @@
         <v>425</v>
       </c>
       <c r="J267" s="5">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>22</v>
@@ -15169,7 +15169,7 @@
         <v>431</v>
       </c>
       <c r="J268" s="2">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>22</v>
@@ -15210,7 +15210,7 @@
         <v>437</v>
       </c>
       <c r="J269" s="5">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>22</v>
@@ -15251,7 +15251,7 @@
         <v>443</v>
       </c>
       <c r="J270" s="2">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>22</v>
@@ -15292,7 +15292,7 @@
         <v>449</v>
       </c>
       <c r="J271" s="5">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>22</v>
@@ -15333,7 +15333,7 @@
         <v>457</v>
       </c>
       <c r="J272" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>22</v>
@@ -15374,7 +15374,7 @@
         <v>463</v>
       </c>
       <c r="J273" s="5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>22</v>
@@ -15415,7 +15415,7 @@
         <v>469</v>
       </c>
       <c r="J274" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K274" s="4" t="s">
         <v>22</v>
@@ -15456,7 +15456,7 @@
         <v>475</v>
       </c>
       <c r="J275" s="5">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>22</v>
@@ -15497,7 +15497,7 @@
         <v>481</v>
       </c>
       <c r="J276" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>22</v>
@@ -15538,7 +15538,7 @@
         <v>487</v>
       </c>
       <c r="J277" s="5">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>22</v>
@@ -15579,7 +15579,7 @@
         <v>493</v>
       </c>
       <c r="J278" s="2">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>22</v>
@@ -15620,7 +15620,7 @@
         <v>499</v>
       </c>
       <c r="J279" s="5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>22</v>
@@ -15661,7 +15661,7 @@
         <v>505</v>
       </c>
       <c r="J280" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>22</v>
@@ -15702,7 +15702,7 @@
         <v>511</v>
       </c>
       <c r="J281" s="5">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>22</v>
@@ -15743,7 +15743,7 @@
         <v>519</v>
       </c>
       <c r="J282" s="2">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>22</v>
@@ -15784,7 +15784,7 @@
         <v>525</v>
       </c>
       <c r="J283" s="5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>22</v>
@@ -15825,7 +15825,7 @@
         <v>531</v>
       </c>
       <c r="J284" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>22</v>
@@ -15866,7 +15866,7 @@
         <v>537</v>
       </c>
       <c r="J285" s="5">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>22</v>
@@ -15907,7 +15907,7 @@
         <v>543</v>
       </c>
       <c r="J286" s="2">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>22</v>
@@ -15948,7 +15948,7 @@
         <v>549</v>
       </c>
       <c r="J287" s="5">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>22</v>
@@ -15989,7 +15989,7 @@
         <v>555</v>
       </c>
       <c r="J288" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>22</v>
@@ -16030,7 +16030,7 @@
         <v>561</v>
       </c>
       <c r="J289" s="5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>22</v>
@@ -16071,7 +16071,7 @@
         <v>567</v>
       </c>
       <c r="J290" s="2">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>22</v>
@@ -16112,7 +16112,7 @@
         <v>573</v>
       </c>
       <c r="J291" s="5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>22</v>
@@ -16153,7 +16153,7 @@
         <v>581</v>
       </c>
       <c r="J292" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>22</v>
@@ -16194,7 +16194,7 @@
         <v>587</v>
       </c>
       <c r="J293" s="5">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>22</v>
@@ -16235,7 +16235,7 @@
         <v>593</v>
       </c>
       <c r="J294" s="2">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>22</v>
@@ -16276,7 +16276,7 @@
         <v>599</v>
       </c>
       <c r="J295" s="5">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>22</v>
@@ -16317,7 +16317,7 @@
         <v>605</v>
       </c>
       <c r="J296" s="2">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>22</v>
@@ -16358,7 +16358,7 @@
         <v>611</v>
       </c>
       <c r="J297" s="5">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>22</v>
@@ -16399,7 +16399,7 @@
         <v>617</v>
       </c>
       <c r="J298" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>22</v>
@@ -16440,7 +16440,7 @@
         <v>623</v>
       </c>
       <c r="J299" s="5">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>22</v>
@@ -16481,7 +16481,7 @@
         <v>629</v>
       </c>
       <c r="J300" s="2">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K300" s="4" t="s">
         <v>22</v>
@@ -16522,7 +16522,7 @@
         <v>635</v>
       </c>
       <c r="J301" s="5">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>22</v>
